--- a/revision_204/Supplementary_Data_S1_Revised_204.xlsx
+++ b/revision_204/Supplementary_Data_S1_Revised_204.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readme" sheetId="1" r:id="R6c76a20533764867"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" r:id="R6694f0e6611c465d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" r:id="R8d7d8326a8fb4c99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="4" r:id="R1ff6deaa29b241bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary" sheetId="5" r:id="R52d2aab3774142fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readme" sheetId="1" r:id="R7a9dec9c78e943c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" r:id="Rd0eef7e4227740d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" r:id="R52dcb82677fe417d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="4" r:id="R1ce467d9f858449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dictionary" sheetId="5" r:id="Red22ff514bf44565"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +24,7 @@
     <x:numFmt numFmtId="203" formatCode="0.0%"/>
     <x:numFmt numFmtId="204" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -47,6 +47,11 @@
     <x:font>
       <x:b/>
       <x:sz val="12"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -75,7 +80,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -114,6 +119,9 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -124,7 +132,7 @@
         <x:b/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -471,7 +479,7 @@
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="2" t="str">
-        <x:v>Source: author-uploaded marshall_metadata_sari(1).xlsx and final refinery clarification, 14 October 2026.</x:v>
+        <x:v>Source: uploaded workbook, 14 October refinery clarification and author-confirmed layer corrections, 15 October 2026.</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -481,7 +489,7 @@
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="2" t="str">
-        <x:v>204 designs: 65 base, 72 binder, 67 wearing. 60 quarries. Dates 2011–2026. Stable file_name is the join key.</x:v>
+        <x:v>204 designs: 62 base, 75 binder, 67 wearing. 60 quarries. Dates 2011–2026. Stable file_name is the join key.</x:v>
       </x:c>
       <x:c r="B5" s="2"/>
       <x:c r="C5" s="2"/>
@@ -581,7 +589,7 @@
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
       <x:c r="A15" s="2" t="str">
-        <x:v>Audit retains source corrections and the complete gradation-envelope check. Three records remain flagged.</x:v>
+        <x:v>Records 47, 51 and 57 corrected from base to binder after author confirmation. All 204 pass the available-sieve envelope screen.</x:v>
       </x:c>
       <x:c r="B15" s="2"/>
       <x:c r="C15" s="2"/>
@@ -641,7 +649,7 @@
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
       <x:c r="A21" s="2" t="str">
-        <x:v>Data measurements are copied from the latest uploaded source. Changing this workbook does not retrain models.</x:v>
+        <x:v>Measured values are preserved; the three layer labels were corrected. Changing this workbook does not retrain models.</x:v>
       </x:c>
       <x:c r="B21" s="2"/>
       <x:c r="C21" s="2"/>
@@ -1012,7 +1020,7 @@
       </x:c>
       <x:c r="AJ2" s="2"/>
       <x:c r="AK2" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL2" s="2" t="n">
         <x:v>1</x:v>
@@ -1232,7 +1240,7 @@
       </x:c>
       <x:c r="AJ4" s="2"/>
       <x:c r="AK4" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL4" s="2" t="n">
         <x:v>5</x:v>
@@ -1342,7 +1350,7 @@
       </x:c>
       <x:c r="AJ5" s="2"/>
       <x:c r="AK5" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL5" s="2" t="n">
         <x:v>5</x:v>
@@ -1452,7 +1460,7 @@
       </x:c>
       <x:c r="AJ6" s="2"/>
       <x:c r="AK6" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL6" s="2" t="n">
         <x:v>2</x:v>
@@ -1562,10 +1570,10 @@
       </x:c>
       <x:c r="AJ7" s="2"/>
       <x:c r="AK7" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL7" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM7" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -1672,10 +1680,10 @@
       </x:c>
       <x:c r="AJ8" s="2"/>
       <x:c r="AK8" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL8" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM8" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -1782,7 +1790,7 @@
       </x:c>
       <x:c r="AJ9" s="2"/>
       <x:c r="AK9" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL9" s="2" t="n">
         <x:v>1</x:v>
@@ -1892,7 +1900,7 @@
       </x:c>
       <x:c r="AJ10" s="2"/>
       <x:c r="AK10" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL10" s="2" t="n">
         <x:v>1</x:v>
@@ -2112,10 +2120,10 @@
       </x:c>
       <x:c r="AJ12" s="2"/>
       <x:c r="AK12" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL12" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM12" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -2335,7 +2343,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL14" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM14" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -2445,7 +2453,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL15" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM15" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -2552,10 +2560,10 @@
       </x:c>
       <x:c r="AJ16" s="2"/>
       <x:c r="AK16" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AL16" s="2" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="AL16" s="2" t="n">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="AM16" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -2662,10 +2670,10 @@
       </x:c>
       <x:c r="AJ17" s="2"/>
       <x:c r="AK17" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL17" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM17" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -2772,7 +2780,7 @@
       </x:c>
       <x:c r="AJ18" s="2"/>
       <x:c r="AK18" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL18" s="2" t="n">
         <x:v>1</x:v>
@@ -2882,7 +2890,7 @@
       </x:c>
       <x:c r="AJ19" s="2"/>
       <x:c r="AK19" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL19" s="2" t="n">
         <x:v>3</x:v>
@@ -2992,7 +3000,7 @@
       </x:c>
       <x:c r="AJ20" s="2"/>
       <x:c r="AK20" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL20" s="2" t="n">
         <x:v>2</x:v>
@@ -3102,10 +3110,10 @@
       </x:c>
       <x:c r="AJ21" s="2"/>
       <x:c r="AK21" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL21" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM21" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -3212,10 +3220,10 @@
       </x:c>
       <x:c r="AJ22" s="2"/>
       <x:c r="AK22" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL22" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM22" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -3322,7 +3330,7 @@
       </x:c>
       <x:c r="AJ23" s="2"/>
       <x:c r="AK23" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL23" s="2" t="n">
         <x:v>4</x:v>
@@ -3432,10 +3440,10 @@
       </x:c>
       <x:c r="AJ24" s="2"/>
       <x:c r="AK24" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AL24" s="2" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="AL24" s="2" t="n">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="AM24" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -3762,7 +3770,7 @@
       </x:c>
       <x:c r="AJ27" s="2"/>
       <x:c r="AK27" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL27" s="2" t="n">
         <x:v>5</x:v>
@@ -3872,7 +3880,7 @@
       </x:c>
       <x:c r="AJ28" s="2"/>
       <x:c r="AK28" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL28" s="2" t="n">
         <x:v>3</x:v>
@@ -3982,7 +3990,7 @@
       </x:c>
       <x:c r="AJ29" s="2"/>
       <x:c r="AK29" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL29" s="2" t="n">
         <x:v>3</x:v>
@@ -4095,7 +4103,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL30" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM30" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -4205,7 +4213,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL31" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM31" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -4312,10 +4320,10 @@
       </x:c>
       <x:c r="AJ32" s="2"/>
       <x:c r="AK32" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL32" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM32" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -4422,7 +4430,7 @@
       </x:c>
       <x:c r="AJ33" s="2"/>
       <x:c r="AK33" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL33" s="2" t="n">
         <x:v>1</x:v>
@@ -4532,7 +4540,7 @@
       </x:c>
       <x:c r="AJ34" s="2"/>
       <x:c r="AK34" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL34" s="2" t="n">
         <x:v>5</x:v>
@@ -5084,7 +5092,7 @@
       </x:c>
       <x:c r="AJ39" s="2"/>
       <x:c r="AK39" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL39" s="2" t="n">
         <x:v>5</x:v>
@@ -5194,10 +5202,10 @@
       </x:c>
       <x:c r="AJ40" s="2"/>
       <x:c r="AK40" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL40" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM40" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -5414,7 +5422,7 @@
       </x:c>
       <x:c r="AJ42" s="2"/>
       <x:c r="AK42" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL42" s="2" t="n">
         <x:v>3</x:v>
@@ -5524,10 +5532,10 @@
       </x:c>
       <x:c r="AJ43" s="2"/>
       <x:c r="AK43" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AL43" s="2" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="AL43" s="2" t="n">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="AM43" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -5634,7 +5642,7 @@
       </x:c>
       <x:c r="AJ44" s="2"/>
       <x:c r="AK44" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL44" s="2" t="n">
         <x:v>1</x:v>
@@ -5744,7 +5752,7 @@
       </x:c>
       <x:c r="AJ45" s="2"/>
       <x:c r="AK45" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL45" s="2" t="n">
         <x:v>3</x:v>
@@ -5854,10 +5862,10 @@
       </x:c>
       <x:c r="AJ46" s="2"/>
       <x:c r="AK46" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL46" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM46" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -5964,7 +5972,7 @@
       </x:c>
       <x:c r="AJ47" s="2"/>
       <x:c r="AK47" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL47" s="2" t="n">
         <x:v>4</x:v>
@@ -6074,10 +6082,10 @@
       </x:c>
       <x:c r="AJ48" s="2"/>
       <x:c r="AK48" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL48" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM48" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -6184,10 +6192,10 @@
       </x:c>
       <x:c r="AJ49" s="2"/>
       <x:c r="AK49" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL49" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM49" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -6294,7 +6302,7 @@
       </x:c>
       <x:c r="AJ50" s="2"/>
       <x:c r="AK50" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL50" s="2" t="n">
         <x:v>5</x:v>
@@ -6404,10 +6412,10 @@
       </x:c>
       <x:c r="AJ51" s="2"/>
       <x:c r="AK51" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL51" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM51" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -6514,7 +6522,7 @@
       </x:c>
       <x:c r="AJ52" s="2"/>
       <x:c r="AK52" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL52" s="2" t="n">
         <x:v>1</x:v>
@@ -6624,10 +6632,10 @@
       </x:c>
       <x:c r="AJ53" s="2"/>
       <x:c r="AK53" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL53" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM53" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -6734,10 +6742,10 @@
       </x:c>
       <x:c r="AJ54" s="2"/>
       <x:c r="AK54" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL54" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM54" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -6844,7 +6852,7 @@
       </x:c>
       <x:c r="AJ55" s="2"/>
       <x:c r="AK55" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL55" s="2" t="n">
         <x:v>2</x:v>
@@ -6954,10 +6962,10 @@
       </x:c>
       <x:c r="AJ56" s="2"/>
       <x:c r="AK56" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL56" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM56" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -7064,7 +7072,7 @@
       </x:c>
       <x:c r="AJ57" s="2"/>
       <x:c r="AK57" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL57" s="2" t="n">
         <x:v>5</x:v>
@@ -7174,7 +7182,7 @@
       </x:c>
       <x:c r="AJ58" s="2"/>
       <x:c r="AK58" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL58" s="2" t="n">
         <x:v>2</x:v>
@@ -7284,7 +7292,7 @@
       </x:c>
       <x:c r="AJ59" s="2"/>
       <x:c r="AK59" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL59" s="2" t="n">
         <x:v>2</x:v>
@@ -7394,10 +7402,10 @@
       </x:c>
       <x:c r="AJ60" s="2"/>
       <x:c r="AK60" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AL60" s="2" t="n">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL60" s="2" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="AM60" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -7504,10 +7512,10 @@
       </x:c>
       <x:c r="AJ61" s="2"/>
       <x:c r="AK61" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL61" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM61" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -7614,10 +7622,10 @@
       </x:c>
       <x:c r="AJ62" s="2"/>
       <x:c r="AK62" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL62" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM62" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -7837,7 +7845,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AL64" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM64" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -8167,7 +8175,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AL67" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM67" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -8387,7 +8395,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AL69" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM69" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -8607,7 +8615,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AL71" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM71" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -8714,7 +8722,7 @@
       </x:c>
       <x:c r="AJ72" s="2"/>
       <x:c r="AK72" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL72" s="2" t="n">
         <x:v>4</x:v>
@@ -8824,10 +8832,10 @@
       </x:c>
       <x:c r="AJ73" s="2"/>
       <x:c r="AK73" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL73" s="2" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="AL73" s="2" t="n">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="AM73" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -8934,10 +8942,10 @@
       </x:c>
       <x:c r="AJ74" s="2"/>
       <x:c r="AK74" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL74" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM74" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -9044,10 +9052,10 @@
       </x:c>
       <x:c r="AJ75" s="2"/>
       <x:c r="AK75" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL75" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM75" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -9154,10 +9162,10 @@
       </x:c>
       <x:c r="AJ76" s="2"/>
       <x:c r="AK76" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL76" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM76" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -9264,7 +9272,7 @@
       </x:c>
       <x:c r="AJ77" s="2"/>
       <x:c r="AK77" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL77" s="2" t="n">
         <x:v>5</x:v>
@@ -9376,7 +9384,7 @@
         <x:v>70-16</x:v>
       </x:c>
       <x:c r="AK78" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL78" s="2" t="n">
         <x:v>2</x:v>
@@ -9486,10 +9494,10 @@
       </x:c>
       <x:c r="AJ79" s="2"/>
       <x:c r="AK79" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL79" s="2" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="AL79" s="2" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="AM79" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -9596,10 +9604,10 @@
       </x:c>
       <x:c r="AJ80" s="2"/>
       <x:c r="AK80" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL80" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM80" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -9706,7 +9714,7 @@
       </x:c>
       <x:c r="AJ81" s="2"/>
       <x:c r="AK81" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL81" s="2" t="n">
         <x:v>5</x:v>
@@ -9818,7 +9826,7 @@
         <x:v>76-16</x:v>
       </x:c>
       <x:c r="AK82" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL82" s="2" t="n">
         <x:v>4</x:v>
@@ -10265,7 +10273,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AL86" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM86" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -10374,7 +10382,7 @@
         <x:v>76-16</x:v>
       </x:c>
       <x:c r="AK87" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL87" s="2" t="n">
         <x:v>3</x:v>
@@ -10484,10 +10492,10 @@
       </x:c>
       <x:c r="AJ88" s="2"/>
       <x:c r="AK88" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL88" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM88" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -10594,7 +10602,7 @@
       </x:c>
       <x:c r="AJ89" s="2"/>
       <x:c r="AK89" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL89" s="2" t="n">
         <x:v>1</x:v>
@@ -10816,7 +10824,7 @@
         <x:v>76-16</x:v>
       </x:c>
       <x:c r="AK91" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL91" s="2" t="n">
         <x:v>4</x:v>
@@ -10926,10 +10934,10 @@
       </x:c>
       <x:c r="AJ92" s="2"/>
       <x:c r="AK92" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL92" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM92" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -11036,10 +11044,10 @@
       </x:c>
       <x:c r="AJ93" s="2"/>
       <x:c r="AK93" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL93" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM93" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -11146,7 +11154,7 @@
       </x:c>
       <x:c r="AJ94" s="2"/>
       <x:c r="AK94" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL94" s="2" t="n">
         <x:v>2</x:v>
@@ -11369,7 +11377,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AL96" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM96" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -11699,7 +11707,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AL99" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM99" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -11916,7 +11924,7 @@
       </x:c>
       <x:c r="AJ101" s="2"/>
       <x:c r="AK101" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL101" s="2" t="n">
         <x:v>2</x:v>
@@ -12026,10 +12034,10 @@
       </x:c>
       <x:c r="AJ102" s="2"/>
       <x:c r="AK102" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL102" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM102" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -12136,7 +12144,7 @@
       </x:c>
       <x:c r="AJ103" s="2"/>
       <x:c r="AK103" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL103" s="2" t="n">
         <x:v>1</x:v>
@@ -12248,7 +12256,7 @@
         <x:v>70-16</x:v>
       </x:c>
       <x:c r="AK104" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL104" s="2" t="n">
         <x:v>5</x:v>
@@ -12358,7 +12366,7 @@
       </x:c>
       <x:c r="AJ105" s="2"/>
       <x:c r="AK105" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL105" s="2" t="n">
         <x:v>1</x:v>
@@ -12468,7 +12476,7 @@
       </x:c>
       <x:c r="AJ106" s="2"/>
       <x:c r="AK106" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL106" s="2" t="n">
         <x:v>5</x:v>
@@ -12578,10 +12586,10 @@
       </x:c>
       <x:c r="AJ107" s="2"/>
       <x:c r="AK107" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL107" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM107" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -12691,7 +12699,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AL108" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM108" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -12910,7 +12918,7 @@
         <x:v>70-16</x:v>
       </x:c>
       <x:c r="AK110" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL110" s="2" t="n">
         <x:v>4</x:v>
@@ -13020,7 +13028,7 @@
       </x:c>
       <x:c r="AJ111" s="2"/>
       <x:c r="AK111" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL111" s="2" t="n">
         <x:v>4</x:v>
@@ -13130,7 +13138,7 @@
       </x:c>
       <x:c r="AJ112" s="2"/>
       <x:c r="AK112" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL112" s="2" t="n">
         <x:v>4</x:v>
@@ -13240,7 +13248,7 @@
       </x:c>
       <x:c r="AJ113" s="2"/>
       <x:c r="AK113" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL113" s="2" t="n">
         <x:v>1</x:v>
@@ -13352,7 +13360,7 @@
         <x:v>70-16</x:v>
       </x:c>
       <x:c r="AK114" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL114" s="2" t="n">
         <x:v>5</x:v>
@@ -13462,7 +13470,7 @@
       </x:c>
       <x:c r="AJ115" s="2"/>
       <x:c r="AK115" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL115" s="2" t="n">
         <x:v>5</x:v>
@@ -13572,10 +13580,10 @@
       </x:c>
       <x:c r="AJ116" s="2"/>
       <x:c r="AK116" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL116" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM116" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -13685,7 +13693,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL117" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM117" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -13792,7 +13800,7 @@
       </x:c>
       <x:c r="AJ118" s="2"/>
       <x:c r="AK118" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL118" s="2" t="n">
         <x:v>3</x:v>
@@ -13902,10 +13910,10 @@
       </x:c>
       <x:c r="AJ119" s="2"/>
       <x:c r="AK119" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL119" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM119" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -14012,10 +14020,10 @@
       </x:c>
       <x:c r="AJ120" s="2"/>
       <x:c r="AK120" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL120" s="2" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="AL120" s="2" t="n">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="AM120" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -14122,7 +14130,7 @@
       </x:c>
       <x:c r="AJ121" s="2"/>
       <x:c r="AK121" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL121" s="2" t="n">
         <x:v>3</x:v>
@@ -14342,7 +14350,7 @@
       </x:c>
       <x:c r="AJ123" s="2"/>
       <x:c r="AK123" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL123" s="2" t="n">
         <x:v>3</x:v>
@@ -14452,10 +14460,10 @@
       </x:c>
       <x:c r="AJ124" s="2"/>
       <x:c r="AK124" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL124" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM124" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -14562,10 +14570,10 @@
       </x:c>
       <x:c r="AJ125" s="2"/>
       <x:c r="AK125" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL125" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM125" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -14672,10 +14680,10 @@
       </x:c>
       <x:c r="AJ126" s="2"/>
       <x:c r="AK126" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL126" s="2" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="AL126" s="2" t="n">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="AM126" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -14782,10 +14790,10 @@
       </x:c>
       <x:c r="AJ127" s="2"/>
       <x:c r="AK127" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL127" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM127" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -14892,7 +14900,7 @@
       </x:c>
       <x:c r="AJ128" s="2"/>
       <x:c r="AK128" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL128" s="2" t="n">
         <x:v>1</x:v>
@@ -15005,7 +15013,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL129" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM129" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -15112,7 +15120,7 @@
       </x:c>
       <x:c r="AJ130" s="2"/>
       <x:c r="AK130" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL130" s="2" t="n">
         <x:v>3</x:v>
@@ -15222,7 +15230,7 @@
       </x:c>
       <x:c r="AJ131" s="2"/>
       <x:c r="AK131" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL131" s="2" t="n">
         <x:v>4</x:v>
@@ -15332,10 +15340,10 @@
       </x:c>
       <x:c r="AJ132" s="2"/>
       <x:c r="AK132" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL132" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM132" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -15442,10 +15450,10 @@
       </x:c>
       <x:c r="AJ133" s="2"/>
       <x:c r="AK133" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL133" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM133" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -15552,7 +15560,7 @@
       </x:c>
       <x:c r="AJ134" s="2"/>
       <x:c r="AK134" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL134" s="2" t="n">
         <x:v>3</x:v>
@@ -15994,10 +16002,10 @@
       </x:c>
       <x:c r="AJ138" s="2"/>
       <x:c r="AK138" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL138" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM138" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -16104,10 +16112,10 @@
       </x:c>
       <x:c r="AJ139" s="2"/>
       <x:c r="AK139" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AL139" s="2" t="n">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL139" s="2" t="n">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="AM139" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -16214,7 +16222,7 @@
       </x:c>
       <x:c r="AJ140" s="2"/>
       <x:c r="AK140" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL140" s="2" t="n">
         <x:v>1</x:v>
@@ -16324,10 +16332,10 @@
       </x:c>
       <x:c r="AJ141" s="2"/>
       <x:c r="AK141" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL141" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM141" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -16434,7 +16442,7 @@
       </x:c>
       <x:c r="AJ142" s="2"/>
       <x:c r="AK142" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL142" s="2" t="n">
         <x:v>2</x:v>
@@ -16544,7 +16552,7 @@
       </x:c>
       <x:c r="AJ143" s="2"/>
       <x:c r="AK143" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL143" s="2" t="n">
         <x:v>4</x:v>
@@ -16654,10 +16662,10 @@
       </x:c>
       <x:c r="AJ144" s="2"/>
       <x:c r="AK144" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL144" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM144" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -16671,7 +16679,7 @@
         <x:v>1 (47).docx</x:v>
       </x:c>
       <x:c r="B145" s="2" t="str">
-        <x:v>ac_base_course</x:v>
+        <x:v>binder_course</x:v>
       </x:c>
       <x:c r="C145" s="7" t="n">
         <x:v>4.3</x:v>
@@ -16764,16 +16772,16 @@
       </x:c>
       <x:c r="AJ145" s="2"/>
       <x:c r="AK145" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL145" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM145" s="2" t="str">
         <x:v>train_2011_2021</x:v>
       </x:c>
       <x:c r="AN145" s="2" t="str">
-        <x:v>author_verification_required</x:v>
+        <x:v>compatible_with_supplied_table</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="22" customHeight="1">
@@ -16874,7 +16882,7 @@
       </x:c>
       <x:c r="AJ146" s="2"/>
       <x:c r="AK146" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL146" s="2" t="n">
         <x:v>1</x:v>
@@ -16984,7 +16992,7 @@
       </x:c>
       <x:c r="AJ147" s="2"/>
       <x:c r="AK147" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL147" s="2" t="n">
         <x:v>4</x:v>
@@ -17097,7 +17105,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL148" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM148" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -17204,7 +17212,7 @@
       </x:c>
       <x:c r="AJ149" s="2"/>
       <x:c r="AK149" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL149" s="2" t="n">
         <x:v>4</x:v>
@@ -17221,7 +17229,7 @@
         <x:v>1 (51).docx</x:v>
       </x:c>
       <x:c r="B150" s="2" t="str">
-        <x:v>ac_base_course</x:v>
+        <x:v>binder_course</x:v>
       </x:c>
       <x:c r="C150" s="7" t="n">
         <x:v>4.25</x:v>
@@ -17314,16 +17322,16 @@
       </x:c>
       <x:c r="AJ150" s="2"/>
       <x:c r="AK150" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL150" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM150" s="2" t="str">
         <x:v>train_2011_2021</x:v>
       </x:c>
       <x:c r="AN150" s="2" t="str">
-        <x:v>author_verification_required</x:v>
+        <x:v>compatible_with_supplied_table</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="22" customHeight="1">
@@ -17424,7 +17432,7 @@
       </x:c>
       <x:c r="AJ151" s="2"/>
       <x:c r="AK151" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL151" s="2" t="n">
         <x:v>5</x:v>
@@ -17534,10 +17542,10 @@
       </x:c>
       <x:c r="AJ152" s="2"/>
       <x:c r="AK152" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL152" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM152" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -17644,7 +17652,7 @@
       </x:c>
       <x:c r="AJ153" s="2"/>
       <x:c r="AK153" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL153" s="2" t="n">
         <x:v>4</x:v>
@@ -17754,10 +17762,10 @@
       </x:c>
       <x:c r="AJ154" s="2"/>
       <x:c r="AK154" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL154" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM154" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -17864,10 +17872,10 @@
       </x:c>
       <x:c r="AJ155" s="2"/>
       <x:c r="AK155" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL155" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM155" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -17881,7 +17889,7 @@
         <x:v>1 (57).docx</x:v>
       </x:c>
       <x:c r="B156" s="2" t="str">
-        <x:v>ac_base_course</x:v>
+        <x:v>binder_course</x:v>
       </x:c>
       <x:c r="C156" s="7" t="n">
         <x:v>4.3</x:v>
@@ -17974,16 +17982,16 @@
       </x:c>
       <x:c r="AJ156" s="2"/>
       <x:c r="AK156" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL156" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM156" s="2" t="str">
         <x:v>train_2011_2021</x:v>
       </x:c>
       <x:c r="AN156" s="2" t="str">
-        <x:v>author_verification_required</x:v>
+        <x:v>compatible_with_supplied_table</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="22" customHeight="1">
@@ -18084,7 +18092,7 @@
       </x:c>
       <x:c r="AJ157" s="2"/>
       <x:c r="AK157" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL157" s="2" t="n">
         <x:v>5</x:v>
@@ -18194,7 +18202,7 @@
       </x:c>
       <x:c r="AJ158" s="2"/>
       <x:c r="AK158" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL158" s="2" t="n">
         <x:v>5</x:v>
@@ -18306,7 +18314,7 @@
         <x:v>82-16</x:v>
       </x:c>
       <x:c r="AK159" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL159" s="2" t="n">
         <x:v>5</x:v>
@@ -18416,7 +18424,7 @@
       </x:c>
       <x:c r="AJ160" s="2"/>
       <x:c r="AK160" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL160" s="2" t="n">
         <x:v>5</x:v>
@@ -18526,7 +18534,7 @@
       </x:c>
       <x:c r="AJ161" s="2"/>
       <x:c r="AK161" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL161" s="2" t="n">
         <x:v>4</x:v>
@@ -18636,7 +18644,7 @@
       </x:c>
       <x:c r="AJ162" s="2"/>
       <x:c r="AK162" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL162" s="2" t="n">
         <x:v>1</x:v>
@@ -18746,7 +18754,7 @@
       </x:c>
       <x:c r="AJ163" s="2"/>
       <x:c r="AK163" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL163" s="2" t="n">
         <x:v>1</x:v>
@@ -18856,7 +18864,7 @@
       </x:c>
       <x:c r="AJ164" s="2"/>
       <x:c r="AK164" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL164" s="2" t="n">
         <x:v>1</x:v>
@@ -18969,7 +18977,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AL165" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM165" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -19186,7 +19194,7 @@
       </x:c>
       <x:c r="AJ167" s="2"/>
       <x:c r="AK167" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL167" s="2" t="n">
         <x:v>2</x:v>
@@ -19296,10 +19304,10 @@
       </x:c>
       <x:c r="AJ168" s="2"/>
       <x:c r="AK168" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL168" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM168" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -19406,7 +19414,7 @@
       </x:c>
       <x:c r="AJ169" s="2"/>
       <x:c r="AK169" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL169" s="2" t="n">
         <x:v>5</x:v>
@@ -19516,10 +19524,10 @@
       </x:c>
       <x:c r="AJ170" s="2"/>
       <x:c r="AK170" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL170" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM170" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -19626,7 +19634,7 @@
       </x:c>
       <x:c r="AJ171" s="2"/>
       <x:c r="AK171" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL171" s="2" t="n">
         <x:v>1</x:v>
@@ -19736,10 +19744,10 @@
       </x:c>
       <x:c r="AJ172" s="2"/>
       <x:c r="AK172" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL172" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM172" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -19846,10 +19854,10 @@
       </x:c>
       <x:c r="AJ173" s="2"/>
       <x:c r="AK173" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL173" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM173" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -20066,10 +20074,10 @@
       </x:c>
       <x:c r="AJ175" s="2"/>
       <x:c r="AK175" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL175" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM175" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -20176,7 +20184,7 @@
       </x:c>
       <x:c r="AJ176" s="2"/>
       <x:c r="AK176" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL176" s="2" t="n">
         <x:v>2</x:v>
@@ -20286,10 +20294,10 @@
       </x:c>
       <x:c r="AJ177" s="2"/>
       <x:c r="AK177" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AL177" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AM177" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -20396,7 +20404,7 @@
       </x:c>
       <x:c r="AJ178" s="2"/>
       <x:c r="AK178" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL178" s="2" t="n">
         <x:v>3</x:v>
@@ -20506,7 +20514,7 @@
       </x:c>
       <x:c r="AJ179" s="2"/>
       <x:c r="AK179" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL179" s="2" t="n">
         <x:v>1</x:v>
@@ -20616,10 +20624,10 @@
       </x:c>
       <x:c r="AJ180" s="2"/>
       <x:c r="AK180" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL180" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM180" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -20726,7 +20734,7 @@
       </x:c>
       <x:c r="AJ181" s="2"/>
       <x:c r="AK181" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL181" s="2" t="n">
         <x:v>3</x:v>
@@ -20836,10 +20844,10 @@
       </x:c>
       <x:c r="AJ182" s="2"/>
       <x:c r="AK182" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL182" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM182" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -20949,7 +20957,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AL183" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM183" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -21059,7 +21067,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AL184" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM184" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -21166,7 +21174,7 @@
       </x:c>
       <x:c r="AJ185" s="2"/>
       <x:c r="AK185" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL185" s="2" t="n">
         <x:v>4</x:v>
@@ -21276,7 +21284,7 @@
       </x:c>
       <x:c r="AJ186" s="2"/>
       <x:c r="AK186" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL186" s="2" t="n">
         <x:v>3</x:v>
@@ -21386,10 +21394,10 @@
       </x:c>
       <x:c r="AJ187" s="2"/>
       <x:c r="AK187" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL187" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM187" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -21496,7 +21504,7 @@
       </x:c>
       <x:c r="AJ188" s="2"/>
       <x:c r="AK188" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL188" s="2" t="n">
         <x:v>3</x:v>
@@ -21606,7 +21614,7 @@
       </x:c>
       <x:c r="AJ189" s="2"/>
       <x:c r="AK189" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL189" s="2" t="n">
         <x:v>4</x:v>
@@ -21828,7 +21836,7 @@
       </x:c>
       <x:c r="AJ191" s="2"/>
       <x:c r="AK191" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL191" s="2" t="n">
         <x:v>2</x:v>
@@ -21938,7 +21946,7 @@
       </x:c>
       <x:c r="AJ192" s="2"/>
       <x:c r="AK192" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL192" s="2" t="n">
         <x:v>5</x:v>
@@ -22048,10 +22056,10 @@
       </x:c>
       <x:c r="AJ193" s="2"/>
       <x:c r="AK193" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL193" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AM193" s="2" t="str">
         <x:v>train_2011_2021</x:v>
@@ -22158,7 +22166,7 @@
       </x:c>
       <x:c r="AJ194" s="2"/>
       <x:c r="AK194" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL194" s="2" t="n">
         <x:v>2</x:v>
@@ -22378,7 +22386,7 @@
       </x:c>
       <x:c r="AJ196" s="2"/>
       <x:c r="AK196" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL196" s="2" t="n">
         <x:v>2</x:v>
@@ -22488,7 +22496,7 @@
       </x:c>
       <x:c r="AJ197" s="2"/>
       <x:c r="AK197" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL197" s="2" t="n">
         <x:v>5</x:v>
@@ -22598,7 +22606,7 @@
       </x:c>
       <x:c r="AJ198" s="2"/>
       <x:c r="AK198" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL198" s="2" t="n">
         <x:v>4</x:v>
@@ -22708,7 +22716,7 @@
       </x:c>
       <x:c r="AJ199" s="2"/>
       <x:c r="AK199" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL199" s="2" t="n">
         <x:v>1</x:v>
@@ -22818,7 +22826,7 @@
       </x:c>
       <x:c r="AJ200" s="2"/>
       <x:c r="AK200" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL200" s="2" t="n">
         <x:v>2</x:v>
@@ -22928,7 +22936,7 @@
       </x:c>
       <x:c r="AJ201" s="2"/>
       <x:c r="AK201" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL201" s="2" t="n">
         <x:v>4</x:v>
@@ -23038,10 +23046,10 @@
       </x:c>
       <x:c r="AJ202" s="2"/>
       <x:c r="AK202" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL202" s="2" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="AL202" s="2" t="n">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="AM202" s="2" t="str">
         <x:v>test_2022_2026</x:v>
@@ -23260,7 +23268,7 @@
         <x:v>76-16</x:v>
       </x:c>
       <x:c r="AK204" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL204" s="2" t="n">
         <x:v>2</x:v>
@@ -23387,7 +23395,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fd7c2cd22b74da1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e8ba661eac047f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23458,19 +23466,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E2" s="9" t="n">
-        <x:v>0.906821039306092</x:v>
+        <x:v>0.906079318243074</x:v>
       </x:c>
       <x:c r="F2" s="9" t="n">
-        <x:v>0.072937829221194</x:v>
+        <x:v>0.072691466740198</x:v>
       </x:c>
       <x:c r="G2" s="9" t="n">
-        <x:v>0.103939918726945</x:v>
+        <x:v>0.104352788825058</x:v>
       </x:c>
       <x:c r="H2" s="9" t="n">
-        <x:v>-0.003488605660016</x:v>
+        <x:v>-0.004653722250107</x:v>
       </x:c>
       <x:c r="I2" s="10" t="n">
-        <x:v>0.725490196078431</x:v>
+        <x:v>0.720588235294118</x:v>
       </x:c>
       <x:c r="J2" s="10" t="n">
         <x:v>0.970588235294118</x:v>
@@ -23493,22 +23501,22 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E3" s="9" t="n">
-        <x:v>0.899181566071676</x:v>
+        <x:v>0.910472547400874</x:v>
       </x:c>
       <x:c r="F3" s="9" t="n">
-        <x:v>0.074005912142278</x:v>
+        <x:v>0.069905662198029</x:v>
       </x:c>
       <x:c r="G3" s="9" t="n">
-        <x:v>0.108116857814019</x:v>
+        <x:v>0.101882960355441</x:v>
       </x:c>
       <x:c r="H3" s="9" t="n">
-        <x:v>-0.000730159790322</x:v>
+        <x:v>-0.000575919132839</x:v>
       </x:c>
       <x:c r="I3" s="10" t="n">
-        <x:v>0.71078431372549</x:v>
+        <x:v>0.720588235294118</x:v>
       </x:c>
       <x:c r="J3" s="10" t="n">
-        <x:v>0.955882352941176</x:v>
+        <x:v>0.970588235294118</x:v>
       </x:c>
       <x:c r="K3" s="10" t="n">
         <x:v>0.995098039215686</x:v>
@@ -23525,25 +23533,25 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D4" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E4" s="9" t="n">
-        <x:v>0.14331047491134</x:v>
+        <x:v>-0.131863610416321</x:v>
       </x:c>
       <x:c r="F4" s="9" t="n">
-        <x:v>0.079463024572168</x:v>
+        <x:v>0.077074582907547</x:v>
       </x:c>
       <x:c r="G4" s="9" t="n">
-        <x:v>0.109060981304067</x:v>
+        <x:v>0.108905569444723</x:v>
       </x:c>
       <x:c r="H4" s="9" t="n">
-        <x:v>-0.016801998218766</x:v>
+        <x:v>-0.016005801058204</x:v>
       </x:c>
       <x:c r="I4" s="10" t="n">
-        <x:v>0.661538461538462</x:v>
+        <x:v>0.661290322580645</x:v>
       </x:c>
       <x:c r="J4" s="10" t="n">
-        <x:v>0.953846153846154</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K4" s="10" t="n">
         <x:v>1</x:v>
@@ -23560,25 +23568,25 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D5" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
-        <x:v>-0.057461177812126</x:v>
+        <x:v>-0.033624019602676</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>0.085338148933795</x:v>
+        <x:v>0.073794782429101</x:v>
       </x:c>
       <x:c r="G5" s="9" t="n">
-        <x:v>0.121168543861064</x:v>
+        <x:v>0.104072104783999</x:v>
       </x:c>
       <x:c r="H5" s="9" t="n">
-        <x:v>-0.000513788098694</x:v>
+        <x:v>-0.000420690856988</x:v>
       </x:c>
       <x:c r="I5" s="10" t="n">
-        <x:v>0.584615384615385</x:v>
+        <x:v>0.741935483870968</x:v>
       </x:c>
       <x:c r="J5" s="10" t="n">
-        <x:v>0.907692307692308</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K5" s="10" t="n">
         <x:v>1</x:v>
@@ -23595,28 +23603,28 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D6" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E6" s="9" t="n">
-        <x:v>-0.078308809731923</x:v>
+        <x:v>-0.117945923550645</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:v>0.084271140236682</x:v>
+        <x:v>0.084210625854251</x:v>
       </x:c>
       <x:c r="G6" s="9" t="n">
-        <x:v>0.119688967834404</x:v>
+        <x:v>0.119726985530388</x:v>
       </x:c>
       <x:c r="H6" s="9" t="n">
-        <x:v>0.002377379893161</x:v>
+        <x:v>-0.000716602597641</x:v>
       </x:c>
       <x:c r="I6" s="10" t="n">
-        <x:v>0.666666666666667</x:v>
+        <x:v>0.693333333333333</x:v>
       </x:c>
       <x:c r="J6" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K6" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -23630,28 +23638,28 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D7" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E7" s="9" t="n">
-        <x:v>-0.071277974693311</x:v>
+        <x:v>-0.079796229013378</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:v>0.084679537958728</x:v>
+        <x:v>0.082156639174174</x:v>
       </x:c>
       <x:c r="G7" s="9" t="n">
-        <x:v>0.119298129148253</x:v>
+        <x:v>0.117666423431356</x:v>
       </x:c>
       <x:c r="H7" s="9" t="n">
-        <x:v>-0.001641893103758</x:v>
+        <x:v>-0.001067707608524</x:v>
       </x:c>
       <x:c r="I7" s="10" t="n">
-        <x:v>0.694444444444444</x:v>
+        <x:v>0.666666666666667</x:v>
       </x:c>
       <x:c r="J7" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K7" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
@@ -23668,19 +23676,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E8" s="9" t="n">
-        <x:v>-0.004757691685113</x:v>
+        <x:v>-0.034113087480392</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:v>0.054428335326738</x:v>
+        <x:v>0.055740867696472</x:v>
       </x:c>
       <x:c r="G8" s="9" t="n">
-        <x:v>0.077204293002415</x:v>
+        <x:v>0.078323989002076</x:v>
       </x:c>
       <x:c r="H8" s="9" t="n">
-        <x:v>0.003123626526403</x:v>
+        <x:v>0.001443963006116</x:v>
       </x:c>
       <x:c r="I8" s="10" t="n">
-        <x:v>0.850746268656716</x:v>
+        <x:v>0.805970149253731</x:v>
       </x:c>
       <x:c r="J8" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -23703,19 +23711,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E9" s="9" t="n">
-        <x:v>-0.020429942959652</x:v>
+        <x:v>-0.0255600349513</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>0.051541786019398</x:v>
+        <x:v>0.052592994622845</x:v>
       </x:c>
       <x:c r="G9" s="9" t="n">
-        <x:v>0.077804081021607</x:v>
+        <x:v>0.077999411280562</x:v>
       </x:c>
       <x:c r="H9" s="9" t="n">
-        <x:v>0.000039700487462</x:v>
+        <x:v>-0.000169053721292</x:v>
       </x:c>
       <x:c r="I9" s="10" t="n">
-        <x:v>0.850746268656716</x:v>
+        <x:v>0.761194029850746</x:v>
       </x:c>
       <x:c r="J9" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -23738,19 +23746,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E10" s="9" t="n">
-        <x:v>0.91049211395524</x:v>
+        <x:v>0.912148235720792</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>0.071155137117896</x:v>
+        <x:v>0.069901136091814</x:v>
       </x:c>
       <x:c r="G10" s="9" t="n">
-        <x:v>0.101871826299024</x:v>
+        <x:v>0.100924983173146</x:v>
       </x:c>
       <x:c r="H10" s="9" t="n">
-        <x:v>0.000336121103185</x:v>
+        <x:v>-0.000353229834125</x:v>
       </x:c>
       <x:c r="I10" s="10" t="n">
-        <x:v>0.720588235294118</x:v>
+        <x:v>0.740196078431373</x:v>
       </x:c>
       <x:c r="J10" s="10" t="n">
         <x:v>0.970588235294118</x:v>
@@ -23773,22 +23781,22 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E11" s="9" t="n">
-        <x:v>0.899554621490559</x:v>
+        <x:v>0.912988200714348</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:v>0.074028281278023</x:v>
+        <x:v>0.068959561812146</x:v>
       </x:c>
       <x:c r="G11" s="9" t="n">
-        <x:v>0.107916641650263</x:v>
+        <x:v>0.10044134427722</x:v>
       </x:c>
       <x:c r="H11" s="9" t="n">
-        <x:v>0.00009816980309</x:v>
+        <x:v>-0.000034294290742</x:v>
       </x:c>
       <x:c r="I11" s="10" t="n">
-        <x:v>0.691176470588235</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="J11" s="10" t="n">
-        <x:v>0.96078431372549</x:v>
+        <x:v>0.970588235294118</x:v>
       </x:c>
       <x:c r="K11" s="10" t="n">
         <x:v>0.995098039215686</x:v>
@@ -23805,25 +23813,25 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D12" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E12" s="9" t="n">
-        <x:v>0.223472751101417</x:v>
+        <x:v>-0.0654346673098</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
-        <x:v>0.074357571598877</x:v>
+        <x:v>0.074405218307741</x:v>
       </x:c>
       <x:c r="G12" s="9" t="n">
-        <x:v>0.103833148382639</x:v>
+        <x:v>0.105661422534816</x:v>
       </x:c>
       <x:c r="H12" s="9" t="n">
-        <x:v>-0.012559647114185</x:v>
+        <x:v>-0.011342237623339</x:v>
       </x:c>
       <x:c r="I12" s="10" t="n">
-        <x:v>0.707692307692308</x:v>
+        <x:v>0.693548387096774</x:v>
       </x:c>
       <x:c r="J12" s="10" t="n">
-        <x:v>0.953846153846154</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K12" s="10" t="n">
         <x:v>1</x:v>
@@ -23840,25 +23848,25 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D13" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E13" s="9" t="n">
-        <x:v>-0.023589328332767</x:v>
+        <x:v>-0.032963387565673</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
-        <x:v>0.082455621301775</x:v>
+        <x:v>0.073558262014483</x:v>
       </x:c>
       <x:c r="G13" s="9" t="n">
-        <x:v>0.11921215735628</x:v>
+        <x:v>0.104038841065969</x:v>
       </x:c>
       <x:c r="H13" s="9" t="n">
-        <x:v>-1.29810692110018e-16</x:v>
+        <x:v>-0.000026333113891</x:v>
       </x:c>
       <x:c r="I13" s="10" t="n">
-        <x:v>0.646153846153846</x:v>
+        <x:v>0.741935483870968</x:v>
       </x:c>
       <x:c r="J13" s="10" t="n">
-        <x:v>0.923076923076923</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K13" s="10" t="n">
         <x:v>1</x:v>
@@ -23875,28 +23883,28 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E14" s="9" t="n">
-        <x:v>-0.053755516435406</x:v>
+        <x:v>-0.016696095776692</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
-        <x:v>0.083244885054461</x:v>
+        <x:v>0.079487708029869</x:v>
       </x:c>
       <x:c r="G14" s="9" t="n">
-        <x:v>0.11831845108629</x:v>
+        <x:v>0.11417663190213</x:v>
       </x:c>
       <x:c r="H14" s="9" t="n">
-        <x:v>0.008382462972126</x:v>
+        <x:v>0.005186068069727</x:v>
       </x:c>
       <x:c r="I14" s="10" t="n">
-        <x:v>0.638888888888889</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="J14" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K14" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
@@ -23910,28 +23918,28 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D15" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E15" s="9" t="n">
-        <x:v>-0.081751134864246</x:v>
+        <x:v>-0.013648180242635</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
-        <x:v>0.085526315789474</x:v>
+        <x:v>0.079422222222222</x:v>
       </x:c>
       <x:c r="G15" s="9" t="n">
-        <x:v>0.119879859369721</x:v>
+        <x:v>0.114005360497751</x:v>
       </x:c>
       <x:c r="H15" s="9" t="n">
-        <x:v>0.000320125025207</x:v>
+        <x:v>5.9211894646675e-17</x:v>
       </x:c>
       <x:c r="I15" s="10" t="n">
-        <x:v>0.638888888888889</x:v>
+        <x:v>0.706666666666667</x:v>
       </x:c>
       <x:c r="J15" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K15" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
@@ -23948,19 +23956,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E16" s="9" t="n">
-        <x:v>-0.027399276257141</x:v>
+        <x:v>-0.026517149446761</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
-        <x:v>0.055056329764219</x:v>
+        <x:v>0.055001942170296</x:v>
       </x:c>
       <x:c r="G16" s="9" t="n">
-        <x:v>0.078069322095893</x:v>
+        <x:v>0.078035799670692</x:v>
       </x:c>
       <x:c r="H16" s="9" t="n">
-        <x:v>0.004200125872816</x:v>
+        <x:v>0.003614996138149</x:v>
       </x:c>
       <x:c r="I16" s="10" t="n">
-        <x:v>0.82089552238806</x:v>
+        <x:v>0.850746268656716</x:v>
       </x:c>
       <x:c r="J16" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -23983,19 +23991,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E17" s="9" t="n">
-        <x:v>-0.049933289734741</x:v>
+        <x:v>-0.036982695345106</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
-        <x:v>0.053496406854616</x:v>
+        <x:v>0.052992114897212</x:v>
       </x:c>
       <x:c r="G17" s="9" t="n">
-        <x:v>0.078920828082881</x:v>
+        <x:v>0.07843258613227</x:v>
       </x:c>
       <x:c r="H17" s="9" t="n">
-        <x:v>-0.000045109880368</x:v>
+        <x:v>-0.000080050481346</x:v>
       </x:c>
       <x:c r="I17" s="10" t="n">
-        <x:v>0.791044776119403</x:v>
+        <x:v>0.805970149253731</x:v>
       </x:c>
       <x:c r="J17" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -24018,19 +24026,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="E18" s="9" t="n">
-        <x:v>0.958915743944084</x:v>
+        <x:v>0.960309824901161</x:v>
       </x:c>
       <x:c r="F18" s="9" t="n">
-        <x:v>0.054592340910936</x:v>
+        <x:v>0.052711696336032</x:v>
       </x:c>
       <x:c r="G18" s="9" t="n">
-        <x:v>0.06838818711972</x:v>
+        <x:v>0.067217891464093</x:v>
       </x:c>
       <x:c r="H18" s="9" t="n">
-        <x:v>-0.01808032177943</x:v>
+        <x:v>-0.017866686301463</x:v>
       </x:c>
       <x:c r="I18" s="10" t="n">
-        <x:v>0.80952380952381</x:v>
+        <x:v>0.833333333333333</x:v>
       </x:c>
       <x:c r="J18" s="10" t="n">
         <x:v>1</x:v>
@@ -24053,19 +24061,19 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="E19" s="9" t="n">
-        <x:v>0.959103174490407</x:v>
+        <x:v>0.960426448839022</x:v>
       </x:c>
       <x:c r="F19" s="9" t="n">
-        <x:v>0.053170392825565</x:v>
+        <x:v>0.052877653042842</x:v>
       </x:c>
       <x:c r="G19" s="9" t="n">
-        <x:v>0.068232011868625</x:v>
+        <x:v>0.067119063703084</x:v>
       </x:c>
       <x:c r="H19" s="9" t="n">
-        <x:v>-0.01951338890994</x:v>
+        <x:v>-0.013594542933369</x:v>
       </x:c>
       <x:c r="I19" s="10" t="n">
-        <x:v>0.738095238095238</x:v>
+        <x:v>0.785714285714286</x:v>
       </x:c>
       <x:c r="J19" s="10" t="n">
         <x:v>1</x:v>
@@ -24088,19 +24096,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E20" s="9" t="n">
-        <x:v>-0.073426977776607</x:v>
+        <x:v>-0.006732900386091</x:v>
       </x:c>
       <x:c r="F20" s="9" t="n">
-        <x:v>0.067656225101361</x:v>
+        <x:v>0.064753658105925</x:v>
       </x:c>
       <x:c r="G20" s="9" t="n">
-        <x:v>0.079697170098787</x:v>
+        <x:v>0.077181600207359</x:v>
       </x:c>
       <x:c r="H20" s="9" t="n">
-        <x:v>-0.007045802395368</x:v>
+        <x:v>-0.010346326615547</x:v>
       </x:c>
       <x:c r="I20" s="10" t="n">
-        <x:v>0.615384615384615</x:v>
+        <x:v>0.692307692307692</x:v>
       </x:c>
       <x:c r="J20" s="10" t="n">
         <x:v>1</x:v>
@@ -24123,19 +24131,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="E21" s="9" t="n">
-        <x:v>-0.068906250000002</x:v>
+        <x:v>-0.001665972511454</x:v>
       </x:c>
       <x:c r="F21" s="9" t="n">
-        <x:v>0.064127218934911</x:v>
+        <x:v>0.06436420722135</x:v>
       </x:c>
       <x:c r="G21" s="9" t="n">
-        <x:v>0.079529171083662</x:v>
+        <x:v>0.076987126123951</x:v>
       </x:c>
       <x:c r="H21" s="9" t="n">
-        <x:v>-0.020192307692308</x:v>
+        <x:v>-0.003139717425432</x:v>
       </x:c>
       <x:c r="I21" s="10" t="n">
-        <x:v>0.615384615384615</x:v>
+        <x:v>0.769230769230769</x:v>
       </x:c>
       <x:c r="J21" s="10" t="n">
         <x:v>1</x:v>
@@ -24158,16 +24166,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E22" s="9" t="n">
-        <x:v>-0.210521036034883</x:v>
+        <x:v>-0.222672977140769</x:v>
       </x:c>
       <x:c r="F22" s="9" t="n">
-        <x:v>0.047385207062726</x:v>
+        <x:v>0.047580654278809</x:v>
       </x:c>
       <x:c r="G22" s="9" t="n">
-        <x:v>0.062377563858885</x:v>
+        <x:v>0.062689873852695</x:v>
       </x:c>
       <x:c r="H22" s="9" t="n">
-        <x:v>-0.025942172808124</x:v>
+        <x:v>-0.024649571752934</x:v>
       </x:c>
       <x:c r="I22" s="10" t="n">
         <x:v>0.928571428571429</x:v>
@@ -24193,16 +24201,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E23" s="9" t="n">
-        <x:v>-0.15629541551063</x:v>
+        <x:v>-0.130639911612769</x:v>
       </x:c>
       <x:c r="F23" s="9" t="n">
-        <x:v>0.048522167487685</x:v>
+        <x:v>0.047423887587822</x:v>
       </x:c>
       <x:c r="G23" s="9" t="n">
-        <x:v>0.060964447308</x:v>
+        <x:v>0.060284323964843</x:v>
       </x:c>
       <x:c r="H23" s="9" t="n">
-        <x:v>-0.022413793103448</x:v>
+        <x:v>-0.020491803278688</x:v>
       </x:c>
       <x:c r="I23" s="10" t="n">
         <x:v>0.857142857142857</x:v>
@@ -24228,16 +24236,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E24" s="9" t="n">
-        <x:v>-0.035818043689481</x:v>
+        <x:v>0.000493996415551</x:v>
       </x:c>
       <x:c r="F24" s="9" t="n">
-        <x:v>0.049996966204232</x:v>
+        <x:v>0.047064302055532</x:v>
       </x:c>
       <x:c r="G24" s="9" t="n">
-        <x:v>0.062921592039368</x:v>
+        <x:v>0.061808850969299</x:v>
       </x:c>
       <x:c r="H24" s="9" t="n">
-        <x:v>-0.020305844285502</x:v>
+        <x:v>-0.01805363827455</x:v>
       </x:c>
       <x:c r="I24" s="10" t="n">
         <x:v>0.866666666666667</x:v>
@@ -24298,19 +24306,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E26" s="9" t="n">
-        <x:v>0.906659917725971</x:v>
+        <x:v>0.907204800083544</x:v>
       </x:c>
       <x:c r="F26" s="9" t="n">
-        <x:v>0.074839181353632</x:v>
+        <x:v>0.073671678958756</x:v>
       </x:c>
       <x:c r="G26" s="9" t="n">
-        <x:v>0.104029744426409</x:v>
+        <x:v>0.103725657811136</x:v>
       </x:c>
       <x:c r="H26" s="9" t="n">
-        <x:v>-0.001949074397349</x:v>
+        <x:v>-0.005075578587551</x:v>
       </x:c>
       <x:c r="I26" s="10" t="n">
-        <x:v>0.725490196078431</x:v>
+        <x:v>0.705882352941176</x:v>
       </x:c>
       <x:c r="J26" s="10" t="n">
         <x:v>0.970588235294118</x:v>
@@ -24333,22 +24341,22 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E27" s="9" t="n">
-        <x:v>0.899181566071676</x:v>
+        <x:v>0.910472547400874</x:v>
       </x:c>
       <x:c r="F27" s="9" t="n">
-        <x:v>0.074005912142278</x:v>
+        <x:v>0.069905662198029</x:v>
       </x:c>
       <x:c r="G27" s="9" t="n">
-        <x:v>0.108116857814019</x:v>
+        <x:v>0.101882960355441</x:v>
       </x:c>
       <x:c r="H27" s="9" t="n">
-        <x:v>-0.000730159790322</x:v>
+        <x:v>-0.000575919132839</x:v>
       </x:c>
       <x:c r="I27" s="10" t="n">
-        <x:v>0.71078431372549</x:v>
+        <x:v>0.720588235294118</x:v>
       </x:c>
       <x:c r="J27" s="10" t="n">
-        <x:v>0.955882352941176</x:v>
+        <x:v>0.970588235294118</x:v>
       </x:c>
       <x:c r="K27" s="10" t="n">
         <x:v>0.995098039215686</x:v>
@@ -24365,25 +24373,25 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D28" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E28" s="9" t="n">
-        <x:v>0.135371493979044</x:v>
+        <x:v>-0.10966764503201</x:v>
       </x:c>
       <x:c r="F28" s="9" t="n">
-        <x:v>0.080338585129894</x:v>
+        <x:v>0.077744613291915</x:v>
       </x:c>
       <x:c r="G28" s="9" t="n">
-        <x:v>0.109565152499209</x:v>
+        <x:v>0.107832457556511</x:v>
       </x:c>
       <x:c r="H28" s="9" t="n">
-        <x:v>-0.006956405813244</x:v>
+        <x:v>-0.012649191241967</x:v>
       </x:c>
       <x:c r="I28" s="10" t="n">
-        <x:v>0.661538461538462</x:v>
+        <x:v>0.629032258064516</x:v>
       </x:c>
       <x:c r="J28" s="10" t="n">
-        <x:v>0.953846153846154</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K28" s="10" t="n">
         <x:v>1</x:v>
@@ -24400,25 +24408,25 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D29" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E29" s="9" t="n">
-        <x:v>-0.057461177812126</x:v>
+        <x:v>-0.033624019602676</x:v>
       </x:c>
       <x:c r="F29" s="9" t="n">
-        <x:v>0.085338148933795</x:v>
+        <x:v>0.073794782429101</x:v>
       </x:c>
       <x:c r="G29" s="9" t="n">
-        <x:v>0.121168543861064</x:v>
+        <x:v>0.104072104783999</x:v>
       </x:c>
       <x:c r="H29" s="9" t="n">
-        <x:v>-0.000513788098694</x:v>
+        <x:v>-0.000420690856988</x:v>
       </x:c>
       <x:c r="I29" s="10" t="n">
-        <x:v>0.584615384615385</x:v>
+        <x:v>0.741935483870968</x:v>
       </x:c>
       <x:c r="J29" s="10" t="n">
-        <x:v>0.907692307692308</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K29" s="10" t="n">
         <x:v>1</x:v>
@@ -24435,28 +24443,28 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D30" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E30" s="9" t="n">
-        <x:v>-0.069621710712369</x:v>
+        <x:v>-0.107348419739817</x:v>
       </x:c>
       <x:c r="F30" s="9" t="n">
-        <x:v>0.087037881400207</x:v>
+        <x:v>0.085322217330051</x:v>
       </x:c>
       <x:c r="G30" s="9" t="n">
-        <x:v>0.119205872222676</x:v>
+        <x:v>0.119158161765489</x:v>
       </x:c>
       <x:c r="H30" s="9" t="n">
-        <x:v>-0.00087727863423</x:v>
+        <x:v>-0.003012235495587</x:v>
       </x:c>
       <x:c r="I30" s="10" t="n">
-        <x:v>0.694444444444444</x:v>
+        <x:v>0.666666666666667</x:v>
       </x:c>
       <x:c r="J30" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K30" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
@@ -24470,28 +24478,28 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D31" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E31" s="9" t="n">
-        <x:v>-0.071277974693311</x:v>
+        <x:v>-0.079796229013378</x:v>
       </x:c>
       <x:c r="F31" s="9" t="n">
-        <x:v>0.084679537958728</x:v>
+        <x:v>0.082156639174174</x:v>
       </x:c>
       <x:c r="G31" s="9" t="n">
-        <x:v>0.119298129148253</x:v>
+        <x:v>0.117666423431356</x:v>
       </x:c>
       <x:c r="H31" s="9" t="n">
-        <x:v>-0.001641893103758</x:v>
+        <x:v>-0.001067707608524</x:v>
       </x:c>
       <x:c r="I31" s="10" t="n">
-        <x:v>0.694444444444444</x:v>
+        <x:v>0.666666666666667</x:v>
       </x:c>
       <x:c r="J31" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K31" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
@@ -24508,16 +24516,16 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E32" s="9" t="n">
-        <x:v>-0.017226169647538</x:v>
+        <x:v>-0.029058586457063</x:v>
       </x:c>
       <x:c r="F32" s="9" t="n">
-        <x:v>0.056394888087803</x:v>
+        <x:v>0.056861047518413</x:v>
       </x:c>
       <x:c r="G32" s="9" t="n">
-        <x:v>0.077681846957858</x:v>
+        <x:v>0.078132339933004</x:v>
       </x:c>
       <x:c r="H32" s="9" t="n">
-        <x:v>0.001757003917407</x:v>
+        <x:v>-0.000376873323724</x:v>
       </x:c>
       <x:c r="I32" s="10" t="n">
         <x:v>0.82089552238806</x:v>
@@ -24543,19 +24551,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E33" s="9" t="n">
-        <x:v>-0.020429942959652</x:v>
+        <x:v>-0.0255600349513</x:v>
       </x:c>
       <x:c r="F33" s="9" t="n">
-        <x:v>0.051541786019398</x:v>
+        <x:v>0.052592994622845</x:v>
       </x:c>
       <x:c r="G33" s="9" t="n">
-        <x:v>0.077804081021607</x:v>
+        <x:v>0.077999411280562</x:v>
       </x:c>
       <x:c r="H33" s="9" t="n">
-        <x:v>0.000039700487462</x:v>
+        <x:v>-0.000169053721292</x:v>
       </x:c>
       <x:c r="I33" s="10" t="n">
-        <x:v>0.850746268656716</x:v>
+        <x:v>0.761194029850746</x:v>
       </x:c>
       <x:c r="J33" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -24578,22 +24586,22 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E34" s="9" t="n">
-        <x:v>0.90795717429874</x:v>
+        <x:v>0.906643040025116</x:v>
       </x:c>
       <x:c r="F34" s="9" t="n">
-        <x:v>0.073227041872522</x:v>
+        <x:v>0.073163125905673</x:v>
       </x:c>
       <x:c r="G34" s="9" t="n">
-        <x:v>0.103304303359746</x:v>
+        <x:v>0.104039149301039</x:v>
       </x:c>
       <x:c r="H34" s="9" t="n">
-        <x:v>-0.002305509560491</x:v>
+        <x:v>-0.003536418677204</x:v>
       </x:c>
       <x:c r="I34" s="10" t="n">
-        <x:v>0.725490196078431</x:v>
+        <x:v>0.696078431372549</x:v>
       </x:c>
       <x:c r="J34" s="10" t="n">
-        <x:v>0.975490196078431</x:v>
+        <x:v>0.970588235294118</x:v>
       </x:c>
       <x:c r="K34" s="10" t="n">
         <x:v>0.995098039215686</x:v>
@@ -24613,22 +24621,22 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E35" s="9" t="n">
-        <x:v>0.899181566071676</x:v>
+        <x:v>0.910472547400874</x:v>
       </x:c>
       <x:c r="F35" s="9" t="n">
-        <x:v>0.074005912142278</x:v>
+        <x:v>0.069905662198029</x:v>
       </x:c>
       <x:c r="G35" s="9" t="n">
-        <x:v>0.108116857814019</x:v>
+        <x:v>0.101882960355441</x:v>
       </x:c>
       <x:c r="H35" s="9" t="n">
-        <x:v>-0.000730159790322</x:v>
+        <x:v>-0.000575919132839</x:v>
       </x:c>
       <x:c r="I35" s="10" t="n">
-        <x:v>0.71078431372549</x:v>
+        <x:v>0.720588235294118</x:v>
       </x:c>
       <x:c r="J35" s="10" t="n">
-        <x:v>0.955882352941176</x:v>
+        <x:v>0.970588235294118</x:v>
       </x:c>
       <x:c r="K35" s="10" t="n">
         <x:v>0.995098039215686</x:v>
@@ -24645,25 +24653,25 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D36" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E36" s="9" t="n">
-        <x:v>0.141167717805194</x:v>
+        <x:v>-0.125944687442652</x:v>
       </x:c>
       <x:c r="F36" s="9" t="n">
-        <x:v>0.079077914167189</x:v>
+        <x:v>0.078003208030056</x:v>
       </x:c>
       <x:c r="G36" s="9" t="n">
-        <x:v>0.109197288122847</x:v>
+        <x:v>0.108620442951594</x:v>
       </x:c>
       <x:c r="H36" s="9" t="n">
-        <x:v>-0.015179704760359</x:v>
+        <x:v>-0.015106280471897</x:v>
       </x:c>
       <x:c r="I36" s="10" t="n">
-        <x:v>0.646153846153846</x:v>
+        <x:v>0.629032258064516</x:v>
       </x:c>
       <x:c r="J36" s="10" t="n">
-        <x:v>0.969230769230769</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K36" s="10" t="n">
         <x:v>1</x:v>
@@ -24680,25 +24688,25 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D37" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E37" s="9" t="n">
-        <x:v>-0.057461177812126</x:v>
+        <x:v>-0.033624019602676</x:v>
       </x:c>
       <x:c r="F37" s="9" t="n">
-        <x:v>0.085338148933795</x:v>
+        <x:v>0.073794782429101</x:v>
       </x:c>
       <x:c r="G37" s="9" t="n">
-        <x:v>0.121168543861064</x:v>
+        <x:v>0.104072104783999</x:v>
       </x:c>
       <x:c r="H37" s="9" t="n">
-        <x:v>-0.000513788098694</x:v>
+        <x:v>-0.000420690856988</x:v>
       </x:c>
       <x:c r="I37" s="10" t="n">
-        <x:v>0.584615384615385</x:v>
+        <x:v>0.741935483870968</x:v>
       </x:c>
       <x:c r="J37" s="10" t="n">
-        <x:v>0.907692307692308</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K37" s="10" t="n">
         <x:v>1</x:v>
@@ -24715,28 +24723,28 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D38" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E38" s="9" t="n">
-        <x:v>-0.040992114509942</x:v>
+        <x:v>-0.107897575206319</x:v>
       </x:c>
       <x:c r="F38" s="9" t="n">
-        <x:v>0.083553826512402</x:v>
+        <x:v>0.084070793367524</x:v>
       </x:c>
       <x:c r="G38" s="9" t="n">
-        <x:v>0.117599713835181</x:v>
+        <x:v>0.119187704520041</x:v>
       </x:c>
       <x:c r="H38" s="9" t="n">
-        <x:v>0.004283169623783</x:v>
+        <x:v>0.001321240265396</x:v>
       </x:c>
       <x:c r="I38" s="10" t="n">
-        <x:v>0.680555555555556</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="J38" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K38" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="22" customHeight="1">
@@ -24750,28 +24758,28 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D39" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E39" s="9" t="n">
-        <x:v>-0.071277974693311</x:v>
+        <x:v>-0.079796229013378</x:v>
       </x:c>
       <x:c r="F39" s="9" t="n">
-        <x:v>0.084679537958728</x:v>
+        <x:v>0.082156639174174</x:v>
       </x:c>
       <x:c r="G39" s="9" t="n">
-        <x:v>0.119298129148253</x:v>
+        <x:v>0.117666423431356</x:v>
       </x:c>
       <x:c r="H39" s="9" t="n">
-        <x:v>-0.001641893103758</x:v>
+        <x:v>-0.001067707608524</x:v>
       </x:c>
       <x:c r="I39" s="10" t="n">
-        <x:v>0.694444444444444</x:v>
+        <x:v>0.666666666666667</x:v>
       </x:c>
       <x:c r="J39" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K39" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="22" customHeight="1">
@@ -24788,19 +24796,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E40" s="9" t="n">
-        <x:v>-0.022088291510779</x:v>
+        <x:v>-0.034553689370463</x:v>
       </x:c>
       <x:c r="F40" s="9" t="n">
-        <x:v>0.056453382272152</x:v>
+        <x:v>0.056474168422827</x:v>
       </x:c>
       <x:c r="G40" s="9" t="n">
-        <x:v>0.077867276886649</x:v>
+        <x:v>0.078340672874918</x:v>
       </x:c>
       <x:c r="H40" s="9" t="n">
-        <x:v>0.003104009644341</x:v>
+        <x:v>0.001732342674675</x:v>
       </x:c>
       <x:c r="I40" s="10" t="n">
-        <x:v>0.850746268656716</x:v>
+        <x:v>0.82089552238806</x:v>
       </x:c>
       <x:c r="J40" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -24823,19 +24831,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E41" s="9" t="n">
-        <x:v>-0.020429942959652</x:v>
+        <x:v>-0.0255600349513</x:v>
       </x:c>
       <x:c r="F41" s="9" t="n">
-        <x:v>0.051541786019398</x:v>
+        <x:v>0.052592994622845</x:v>
       </x:c>
       <x:c r="G41" s="9" t="n">
-        <x:v>0.077804081021607</x:v>
+        <x:v>0.077999411280562</x:v>
       </x:c>
       <x:c r="H41" s="9" t="n">
-        <x:v>0.000039700487462</x:v>
+        <x:v>-0.000169053721292</x:v>
       </x:c>
       <x:c r="I41" s="10" t="n">
-        <x:v>0.850746268656716</x:v>
+        <x:v>0.761194029850746</x:v>
       </x:c>
       <x:c r="J41" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -24858,19 +24866,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E42" s="9" t="n">
-        <x:v>0.906105957156453</x:v>
+        <x:v>0.907124109233676</x:v>
       </x:c>
       <x:c r="F42" s="9" t="n">
-        <x:v>0.073470963464184</x:v>
+        <x:v>0.072931144007425</x:v>
       </x:c>
       <x:c r="G42" s="9" t="n">
-        <x:v>0.10433798887902</x:v>
+        <x:v>0.103770745772538</x:v>
       </x:c>
       <x:c r="H42" s="9" t="n">
-        <x:v>-0.002347660591083</x:v>
+        <x:v>-0.004130600755319</x:v>
       </x:c>
       <x:c r="I42" s="10" t="n">
-        <x:v>0.730392156862745</x:v>
+        <x:v>0.71078431372549</x:v>
       </x:c>
       <x:c r="J42" s="10" t="n">
         <x:v>0.970588235294118</x:v>
@@ -24893,22 +24901,22 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E43" s="9" t="n">
-        <x:v>0.899181566071676</x:v>
+        <x:v>0.910472547400874</x:v>
       </x:c>
       <x:c r="F43" s="9" t="n">
-        <x:v>0.074005912142278</x:v>
+        <x:v>0.069905662198029</x:v>
       </x:c>
       <x:c r="G43" s="9" t="n">
-        <x:v>0.108116857814019</x:v>
+        <x:v>0.101882960355441</x:v>
       </x:c>
       <x:c r="H43" s="9" t="n">
-        <x:v>-0.000730159790322</x:v>
+        <x:v>-0.000575919132839</x:v>
       </x:c>
       <x:c r="I43" s="10" t="n">
-        <x:v>0.71078431372549</x:v>
+        <x:v>0.720588235294118</x:v>
       </x:c>
       <x:c r="J43" s="10" t="n">
-        <x:v>0.955882352941176</x:v>
+        <x:v>0.970588235294118</x:v>
       </x:c>
       <x:c r="K43" s="10" t="n">
         <x:v>0.995098039215686</x:v>
@@ -24925,25 +24933,25 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D44" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E44" s="9" t="n">
-        <x:v>0.149133243637313</x:v>
+        <x:v>-0.101661262055678</x:v>
       </x:c>
       <x:c r="F44" s="9" t="n">
-        <x:v>0.078638297473363</x:v>
+        <x:v>0.076417299508755</x:v>
       </x:c>
       <x:c r="G44" s="9" t="n">
-        <x:v>0.108689715172125</x:v>
+        <x:v>0.107442741370246</x:v>
       </x:c>
       <x:c r="H44" s="9" t="n">
-        <x:v>-0.012266430874626</x:v>
+        <x:v>-0.012127795154475</x:v>
       </x:c>
       <x:c r="I44" s="10" t="n">
-        <x:v>0.661538461538462</x:v>
+        <x:v>0.645161290322581</x:v>
       </x:c>
       <x:c r="J44" s="10" t="n">
-        <x:v>0.953846153846154</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K44" s="10" t="n">
         <x:v>1</x:v>
@@ -24960,25 +24968,25 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D45" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E45" s="9" t="n">
-        <x:v>-0.057461177812126</x:v>
+        <x:v>-0.033624019602676</x:v>
       </x:c>
       <x:c r="F45" s="9" t="n">
-        <x:v>0.085338148933795</x:v>
+        <x:v>0.073794782429101</x:v>
       </x:c>
       <x:c r="G45" s="9" t="n">
-        <x:v>0.121168543861064</x:v>
+        <x:v>0.104072104783999</x:v>
       </x:c>
       <x:c r="H45" s="9" t="n">
-        <x:v>-0.000513788098694</x:v>
+        <x:v>-0.000420690856988</x:v>
       </x:c>
       <x:c r="I45" s="10" t="n">
-        <x:v>0.584615384615385</x:v>
+        <x:v>0.741935483870968</x:v>
       </x:c>
       <x:c r="J45" s="10" t="n">
-        <x:v>0.907692307692308</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K45" s="10" t="n">
         <x:v>1</x:v>
@@ -24995,28 +25003,28 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D46" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E46" s="9" t="n">
-        <x:v>-0.086142955551167</x:v>
+        <x:v>-0.112776645393432</x:v>
       </x:c>
       <x:c r="F46" s="9" t="n">
-        <x:v>0.084702905073054</x:v>
+        <x:v>0.084394048917514</x:v>
       </x:c>
       <x:c r="G46" s="9" t="n">
-        <x:v>0.120122964060811</x:v>
+        <x:v>0.119449861577708</x:v>
       </x:c>
       <x:c r="H46" s="9" t="n">
-        <x:v>0.001074658486979</x:v>
+        <x:v>-0.002146802219543</x:v>
       </x:c>
       <x:c r="I46" s="10" t="n">
-        <x:v>0.680555555555556</x:v>
+        <x:v>0.666666666666667</x:v>
       </x:c>
       <x:c r="J46" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K46" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="22" customHeight="1">
@@ -25030,28 +25038,28 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D47" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E47" s="9" t="n">
-        <x:v>-0.071277974693311</x:v>
+        <x:v>-0.079796229013378</x:v>
       </x:c>
       <x:c r="F47" s="9" t="n">
-        <x:v>0.084679537958728</x:v>
+        <x:v>0.082156639174174</x:v>
       </x:c>
       <x:c r="G47" s="9" t="n">
-        <x:v>0.119298129148253</x:v>
+        <x:v>0.117666423431356</x:v>
       </x:c>
       <x:c r="H47" s="9" t="n">
-        <x:v>-0.001641893103758</x:v>
+        <x:v>-0.001067707608524</x:v>
       </x:c>
       <x:c r="I47" s="10" t="n">
-        <x:v>0.694444444444444</x:v>
+        <x:v>0.666666666666667</x:v>
       </x:c>
       <x:c r="J47" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K47" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="22" customHeight="1">
@@ -25068,19 +25076,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E48" s="9" t="n">
-        <x:v>-0.04167871036578</x:v>
+        <x:v>-0.033813656431122</x:v>
       </x:c>
       <x:c r="F48" s="9" t="n">
-        <x:v>0.056387732024852</x:v>
+        <x:v>0.056873539390424</x:v>
       </x:c>
       <x:c r="G48" s="9" t="n">
-        <x:v>0.078609977981398</x:v>
+        <x:v>0.078312648689088</x:v>
       </x:c>
       <x:c r="H48" s="9" t="n">
-        <x:v>0.003597310973243</x:v>
+        <x:v>0.001049118088926</x:v>
       </x:c>
       <x:c r="I48" s="10" t="n">
-        <x:v>0.850746268656716</x:v>
+        <x:v>0.82089552238806</x:v>
       </x:c>
       <x:c r="J48" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -25103,19 +25111,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E49" s="9" t="n">
-        <x:v>-0.020429942959652</x:v>
+        <x:v>-0.0255600349513</x:v>
       </x:c>
       <x:c r="F49" s="9" t="n">
-        <x:v>0.051541786019398</x:v>
+        <x:v>0.052592994622845</x:v>
       </x:c>
       <x:c r="G49" s="9" t="n">
-        <x:v>0.077804081021607</x:v>
+        <x:v>0.077999411280562</x:v>
       </x:c>
       <x:c r="H49" s="9" t="n">
-        <x:v>0.000039700487462</x:v>
+        <x:v>-0.000169053721292</x:v>
       </x:c>
       <x:c r="I49" s="10" t="n">
-        <x:v>0.850746268656716</x:v>
+        <x:v>0.761194029850746</x:v>
       </x:c>
       <x:c r="J49" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -25138,19 +25146,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E50" s="9" t="n">
-        <x:v>0.90713078643049</x:v>
+        <x:v>0.907197018646279</x:v>
       </x:c>
       <x:c r="F50" s="9" t="n">
-        <x:v>0.072824249454845</x:v>
+        <x:v>0.072930070452193</x:v>
       </x:c>
       <x:c r="G50" s="9" t="n">
-        <x:v>0.103767015471048</x:v>
+        <x:v>0.103730006731014</x:v>
       </x:c>
       <x:c r="H50" s="9" t="n">
-        <x:v>-0.001631106844011</x:v>
+        <x:v>-0.001952757685899</x:v>
       </x:c>
       <x:c r="I50" s="10" t="n">
-        <x:v>0.735294117647059</x:v>
+        <x:v>0.715686274509804</x:v>
       </x:c>
       <x:c r="J50" s="10" t="n">
         <x:v>0.970588235294118</x:v>
@@ -25173,22 +25181,22 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="E51" s="9" t="n">
-        <x:v>0.900729802977538</x:v>
+        <x:v>0.911673731372954</x:v>
       </x:c>
       <x:c r="F51" s="9" t="n">
-        <x:v>0.072228529507002</x:v>
+        <x:v>0.069115357116059</x:v>
       </x:c>
       <x:c r="G51" s="9" t="n">
-        <x:v>0.107283487734869</x:v>
+        <x:v>0.101197173793686</x:v>
       </x:c>
       <x:c r="H51" s="9" t="n">
-        <x:v>-0.000480021604057</x:v>
+        <x:v>-0.000492237025771</x:v>
       </x:c>
       <x:c r="I51" s="10" t="n">
-        <x:v>0.637254901960784</x:v>
+        <x:v>0.720588235294118</x:v>
       </x:c>
       <x:c r="J51" s="10" t="n">
-        <x:v>0.955882352941176</x:v>
+        <x:v>0.970588235294118</x:v>
       </x:c>
       <x:c r="K51" s="10" t="n">
         <x:v>0.995098039215686</x:v>
@@ -25205,25 +25213,25 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D52" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E52" s="9" t="n">
-        <x:v>0.187891200805763</x:v>
+        <x:v>-0.09541468983775</x:v>
       </x:c>
       <x:c r="F52" s="9" t="n">
-        <x:v>0.076138108146323</x:v>
+        <x:v>0.076501418989374</x:v>
       </x:c>
       <x:c r="G52" s="9" t="n">
-        <x:v>0.106185393484805</x:v>
+        <x:v>0.107137700723909</x:v>
       </x:c>
       <x:c r="H52" s="9" t="n">
-        <x:v>-0.008834160225333</x:v>
+        <x:v>-0.008948111821501</x:v>
       </x:c>
       <x:c r="I52" s="10" t="n">
-        <x:v>0.707692307692308</x:v>
+        <x:v>0.693548387096774</x:v>
       </x:c>
       <x:c r="J52" s="10" t="n">
-        <x:v>0.953846153846154</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K52" s="10" t="n">
         <x:v>1</x:v>
@@ -25240,25 +25248,25 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D53" s="11" t="n">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E53" s="9" t="n">
-        <x:v>-0.04402453887771</x:v>
+        <x:v>-0.047117711828043</x:v>
       </x:c>
       <x:c r="F53" s="9" t="n">
-        <x:v>0.081650528735983</x:v>
+        <x:v>0.074296230578613</x:v>
       </x:c>
       <x:c r="G53" s="9" t="n">
-        <x:v>0.120396268249552</x:v>
+        <x:v>0.104749219165708</x:v>
       </x:c>
       <x:c r="H53" s="9" t="n">
-        <x:v>-0.000558778863991</x:v>
+        <x:v>-0.000676915774919</x:v>
       </x:c>
       <x:c r="I53" s="10" t="n">
-        <x:v>0.492307692307692</x:v>
+        <x:v>0.741935483870968</x:v>
       </x:c>
       <x:c r="J53" s="10" t="n">
-        <x:v>0.907692307692308</x:v>
+        <x:v>0.951612903225806</x:v>
       </x:c>
       <x:c r="K53" s="10" t="n">
         <x:v>1</x:v>
@@ -25275,28 +25283,28 @@
         <x:v>Extra Trees</x:v>
       </x:c>
       <x:c r="D54" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E54" s="9" t="n">
-        <x:v>-0.102736305926247</x:v>
+        <x:v>-0.119064153159269</x:v>
       </x:c>
       <x:c r="F54" s="9" t="n">
-        <x:v>0.085557077657554</x:v>
+        <x:v>0.085166694143871</x:v>
       </x:c>
       <x:c r="G54" s="9" t="n">
-        <x:v>0.12103706435212</x:v>
+        <x:v>0.119786849247866</x:v>
       </x:c>
       <x:c r="H54" s="9" t="n">
-        <x:v>0.001322358013513</x:v>
+        <x:v>0.000211701678748</x:v>
       </x:c>
       <x:c r="I54" s="10" t="n">
-        <x:v>0.666666666666667</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="J54" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K54" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="22" customHeight="1">
@@ -25310,28 +25318,28 @@
         <x:v>Layer mean</x:v>
       </x:c>
       <x:c r="D55" s="11" t="n">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E55" s="9" t="n">
-        <x:v>-0.038228911527216</x:v>
+        <x:v>-0.035854543460491</x:v>
       </x:c>
       <x:c r="F55" s="9" t="n">
-        <x:v>0.083109483366048</x:v>
+        <x:v>0.080662849420905</x:v>
       </x:c>
       <x:c r="G55" s="9" t="n">
-        <x:v>0.117443532150548</x:v>
+        <x:v>0.11524737370608</x:v>
       </x:c>
       <x:c r="H55" s="9" t="n">
-        <x:v>-0.000718944242322</x:v>
+        <x:v>-0.000648103727884</x:v>
       </x:c>
       <x:c r="I55" s="10" t="n">
-        <x:v>0.694444444444444</x:v>
+        <x:v>0.706666666666667</x:v>
       </x:c>
       <x:c r="J55" s="10" t="n">
-        <x:v>0.972222222222222</x:v>
+        <x:v>0.973333333333333</x:v>
       </x:c>
       <x:c r="K55" s="10" t="n">
-        <x:v>0.986111111111111</x:v>
+        <x:v>0.986666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="22" customHeight="1">
@@ -25348,19 +25356,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E56" s="9" t="n">
-        <x:v>-0.028761247962418</x:v>
+        <x:v>-0.024472604494622</x:v>
       </x:c>
       <x:c r="F56" s="9" t="n">
-        <x:v>0.055926272655724</x:v>
+        <x:v>0.055927527374863</x:v>
       </x:c>
       <x:c r="G56" s="9" t="n">
-        <x:v>0.078121051250782</x:v>
+        <x:v>0.07795804781648</x:v>
       </x:c>
       <x:c r="H56" s="9" t="n">
-        <x:v>0.002183057335753</x:v>
+        <x:v>0.002097652822439</x:v>
       </x:c>
       <x:c r="I56" s="10" t="n">
-        <x:v>0.835820895522388</x:v>
+        <x:v>0.82089552238806</x:v>
       </x:c>
       <x:c r="J56" s="10" t="n">
         <x:v>0.985074626865672</x:v>
@@ -25407,7 +25415,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e58770e7aea413c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae756a1b06f54364"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25605,16 +25613,16 @@
     </x:row>
     <x:row r="13" ht="40" customHeight="1">
       <x:c r="A13" s="12" t="str">
-        <x:v>Unresolved envelope</x:v>
+        <x:v>Layer corrections</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
         <x:v>1 (47), 1 (51), 1 (57).docx</x:v>
       </x:c>
       <x:c r="C13" s="12" t="str">
-        <x:v>19.1 mm values 90.6, 91.5, 90.3 exceed listed 90</x:v>
+        <x:v>ac_base_course to binder_course; measured values retained</x:v>
       </x:c>
       <x:c r="D13" s="12" t="str">
-        <x:v>Retained unchanged; source reports/specification required</x:v>
+        <x:v>Author confirmation 15 October 2026; all 204 compatible with available-sieve layer envelopes</x:v>
       </x:c>
       <x:c r="E13" s="2"/>
     </x:row>
@@ -25666,3064 +25674,3064 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="22" customHeight="1">
-      <x:c r="A19" s="2" t="str">
+      <x:c r="A19" s="14" t="str">
         <x:v>1 (1).docx</x:v>
       </x:c>
-      <x:c r="B19" s="2" t="str">
+      <x:c r="B19" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C19" s="2" t="str">
+      <x:c r="C19" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D19" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E19" s="2"/>
+      <x:c r="D19" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E19" s="14"/>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="2" t="str">
+      <x:c r="A20" s="14" t="str">
         <x:v>1 (10).docx</x:v>
       </x:c>
-      <x:c r="B20" s="2" t="str">
+      <x:c r="B20" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C20" s="2" t="str">
+      <x:c r="C20" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D20" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E20" s="2"/>
+      <x:c r="D20" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E20" s="14"/>
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
-      <x:c r="A21" s="2" t="str">
+      <x:c r="A21" s="14" t="str">
         <x:v>1 (100).docx</x:v>
       </x:c>
-      <x:c r="B21" s="2" t="str">
+      <x:c r="B21" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C21" s="2" t="str">
+      <x:c r="C21" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D21" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E21" s="2"/>
+      <x:c r="D21" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E21" s="14"/>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="2" t="str">
+      <x:c r="A22" s="14" t="str">
         <x:v>1 (101).docx</x:v>
       </x:c>
-      <x:c r="B22" s="2" t="str">
+      <x:c r="B22" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C22" s="2" t="str">
+      <x:c r="C22" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D22" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E22" s="2"/>
+      <x:c r="D22" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E22" s="14"/>
     </x:row>
     <x:row r="23" ht="22" customHeight="1">
-      <x:c r="A23" s="2" t="str">
+      <x:c r="A23" s="14" t="str">
         <x:v>1 (102).docx</x:v>
       </x:c>
-      <x:c r="B23" s="2" t="str">
+      <x:c r="B23" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C23" s="2" t="str">
+      <x:c r="C23" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D23" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E23" s="2"/>
+      <x:c r="D23" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E23" s="14"/>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="2" t="str">
+      <x:c r="A24" s="14" t="str">
         <x:v>1 (103).docx</x:v>
       </x:c>
-      <x:c r="B24" s="2" t="str">
+      <x:c r="B24" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C24" s="2" t="str">
+      <x:c r="C24" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D24" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E24" s="2"/>
+      <x:c r="D24" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E24" s="14"/>
     </x:row>
     <x:row r="25" ht="22" customHeight="1">
-      <x:c r="A25" s="2" t="str">
+      <x:c r="A25" s="14" t="str">
         <x:v>1 (104).docx</x:v>
       </x:c>
-      <x:c r="B25" s="2" t="str">
+      <x:c r="B25" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C25" s="2" t="str">
+      <x:c r="C25" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D25" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E25" s="2"/>
+      <x:c r="D25" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E25" s="14"/>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="2" t="str">
+      <x:c r="A26" s="14" t="str">
         <x:v>1 (105).docx</x:v>
       </x:c>
-      <x:c r="B26" s="2" t="str">
+      <x:c r="B26" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C26" s="2" t="str">
+      <x:c r="C26" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D26" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E26" s="2"/>
+      <x:c r="D26" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E26" s="14"/>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
-      <x:c r="A27" s="2" t="str">
+      <x:c r="A27" s="14" t="str">
         <x:v>1 (106).docx</x:v>
       </x:c>
-      <x:c r="B27" s="2" t="str">
+      <x:c r="B27" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C27" s="2" t="str">
+      <x:c r="C27" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D27" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E27" s="2"/>
+      <x:c r="D27" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E27" s="14"/>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="2" t="str">
+      <x:c r="A28" s="14" t="str">
         <x:v>1 (107).docx</x:v>
       </x:c>
-      <x:c r="B28" s="2" t="str">
+      <x:c r="B28" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C28" s="2" t="str">
+      <x:c r="C28" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D28" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E28" s="2"/>
+      <x:c r="D28" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E28" s="14"/>
     </x:row>
     <x:row r="29" ht="22" customHeight="1">
-      <x:c r="A29" s="2" t="str">
+      <x:c r="A29" s="14" t="str">
         <x:v>1 (108).docx</x:v>
       </x:c>
-      <x:c r="B29" s="2" t="str">
+      <x:c r="B29" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C29" s="2" t="str">
+      <x:c r="C29" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D29" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E29" s="2"/>
+      <x:c r="D29" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E29" s="14"/>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="2" t="str">
+      <x:c r="A30" s="14" t="str">
         <x:v>1 (109).docx</x:v>
       </x:c>
-      <x:c r="B30" s="2" t="str">
+      <x:c r="B30" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C30" s="2" t="str">
+      <x:c r="C30" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D30" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E30" s="2"/>
+      <x:c r="D30" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E30" s="14"/>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
-      <x:c r="A31" s="2" t="str">
+      <x:c r="A31" s="14" t="str">
         <x:v>1 (11).docx</x:v>
       </x:c>
-      <x:c r="B31" s="2" t="str">
+      <x:c r="B31" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C31" s="2" t="str">
+      <x:c r="C31" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D31" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E31" s="2"/>
+      <x:c r="D31" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E31" s="14"/>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="2" t="str">
+      <x:c r="A32" s="14" t="str">
         <x:v>1 (110).docx</x:v>
       </x:c>
-      <x:c r="B32" s="2" t="str">
+      <x:c r="B32" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C32" s="2" t="str">
+      <x:c r="C32" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D32" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E32" s="2"/>
+      <x:c r="D32" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E32" s="14"/>
     </x:row>
     <x:row r="33" ht="22" customHeight="1">
-      <x:c r="A33" s="2" t="str">
+      <x:c r="A33" s="14" t="str">
         <x:v>1 (111).docx</x:v>
       </x:c>
-      <x:c r="B33" s="2" t="str">
+      <x:c r="B33" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C33" s="2" t="str">
+      <x:c r="C33" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D33" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E33" s="2"/>
+      <x:c r="D33" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E33" s="14"/>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="2" t="str">
+      <x:c r="A34" s="14" t="str">
         <x:v>1 (112).docx</x:v>
       </x:c>
-      <x:c r="B34" s="2" t="str">
+      <x:c r="B34" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C34" s="2" t="str">
+      <x:c r="C34" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D34" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E34" s="2"/>
+      <x:c r="D34" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E34" s="14"/>
     </x:row>
     <x:row r="35" ht="22" customHeight="1">
-      <x:c r="A35" s="2" t="str">
+      <x:c r="A35" s="14" t="str">
         <x:v>1 (113).docx</x:v>
       </x:c>
-      <x:c r="B35" s="2" t="str">
+      <x:c r="B35" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C35" s="2" t="str">
+      <x:c r="C35" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D35" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E35" s="2"/>
+      <x:c r="D35" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E35" s="14"/>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
-      <x:c r="A36" s="2" t="str">
+      <x:c r="A36" s="14" t="str">
         <x:v>1 (114).docx</x:v>
       </x:c>
-      <x:c r="B36" s="2" t="str">
+      <x:c r="B36" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C36" s="2" t="str">
+      <x:c r="C36" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D36" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E36" s="2"/>
+      <x:c r="D36" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E36" s="14"/>
     </x:row>
     <x:row r="37" ht="22" customHeight="1">
-      <x:c r="A37" s="2" t="str">
+      <x:c r="A37" s="14" t="str">
         <x:v>1 (115).docx</x:v>
       </x:c>
-      <x:c r="B37" s="2" t="str">
+      <x:c r="B37" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C37" s="2" t="str">
+      <x:c r="C37" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D37" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E37" s="2"/>
+      <x:c r="D37" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E37" s="14"/>
     </x:row>
     <x:row r="38" ht="22" customHeight="1">
-      <x:c r="A38" s="2" t="str">
+      <x:c r="A38" s="14" t="str">
         <x:v>1 (116).docx</x:v>
       </x:c>
-      <x:c r="B38" s="2" t="str">
+      <x:c r="B38" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C38" s="2" t="str">
+      <x:c r="C38" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D38" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E38" s="2"/>
+      <x:c r="D38" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E38" s="14"/>
     </x:row>
     <x:row r="39" ht="22" customHeight="1">
-      <x:c r="A39" s="2" t="str">
+      <x:c r="A39" s="14" t="str">
         <x:v>1 (117).docx</x:v>
       </x:c>
-      <x:c r="B39" s="2" t="str">
+      <x:c r="B39" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C39" s="2" t="str">
+      <x:c r="C39" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D39" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E39" s="2"/>
+      <x:c r="D39" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E39" s="14"/>
     </x:row>
     <x:row r="40" ht="22" customHeight="1">
-      <x:c r="A40" s="2" t="str">
+      <x:c r="A40" s="14" t="str">
         <x:v>1 (118).docx</x:v>
       </x:c>
-      <x:c r="B40" s="2" t="str">
+      <x:c r="B40" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C40" s="2" t="str">
+      <x:c r="C40" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D40" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E40" s="2"/>
+      <x:c r="D40" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E40" s="14"/>
     </x:row>
     <x:row r="41" ht="22" customHeight="1">
-      <x:c r="A41" s="2" t="str">
+      <x:c r="A41" s="14" t="str">
         <x:v>1 (119).docx</x:v>
       </x:c>
-      <x:c r="B41" s="2" t="str">
+      <x:c r="B41" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C41" s="2" t="str">
+      <x:c r="C41" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D41" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E41" s="2"/>
+      <x:c r="D41" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E41" s="14"/>
     </x:row>
     <x:row r="42" ht="22" customHeight="1">
-      <x:c r="A42" s="2" t="str">
+      <x:c r="A42" s="14" t="str">
         <x:v>1 (12).docx</x:v>
       </x:c>
-      <x:c r="B42" s="2" t="str">
+      <x:c r="B42" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C42" s="2" t="str">
+      <x:c r="C42" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D42" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E42" s="2"/>
+      <x:c r="D42" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E42" s="14"/>
     </x:row>
     <x:row r="43" ht="22" customHeight="1">
-      <x:c r="A43" s="2" t="str">
+      <x:c r="A43" s="14" t="str">
         <x:v>1 (120).docx</x:v>
       </x:c>
-      <x:c r="B43" s="2" t="str">
+      <x:c r="B43" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C43" s="2" t="str">
+      <x:c r="C43" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D43" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E43" s="2"/>
+      <x:c r="D43" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E43" s="14"/>
     </x:row>
     <x:row r="44" ht="22" customHeight="1">
-      <x:c r="A44" s="2" t="str">
+      <x:c r="A44" s="14" t="str">
         <x:v>1 (122).docx</x:v>
       </x:c>
-      <x:c r="B44" s="2" t="str">
+      <x:c r="B44" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C44" s="2" t="str">
+      <x:c r="C44" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D44" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E44" s="2"/>
+      <x:c r="D44" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E44" s="14"/>
     </x:row>
     <x:row r="45" ht="22" customHeight="1">
-      <x:c r="A45" s="2" t="str">
+      <x:c r="A45" s="14" t="str">
         <x:v>1 (123).docx</x:v>
       </x:c>
-      <x:c r="B45" s="2" t="str">
+      <x:c r="B45" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C45" s="2" t="str">
+      <x:c r="C45" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D45" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E45" s="2"/>
+      <x:c r="D45" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E45" s="14"/>
     </x:row>
     <x:row r="46" ht="22" customHeight="1">
-      <x:c r="A46" s="2" t="str">
+      <x:c r="A46" s="14" t="str">
         <x:v>1 (124).docx</x:v>
       </x:c>
-      <x:c r="B46" s="2" t="str">
+      <x:c r="B46" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C46" s="2" t="str">
+      <x:c r="C46" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D46" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E46" s="2"/>
+      <x:c r="D46" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E46" s="14"/>
     </x:row>
     <x:row r="47" ht="22" customHeight="1">
-      <x:c r="A47" s="2" t="str">
+      <x:c r="A47" s="14" t="str">
         <x:v>1 (125).docx</x:v>
       </x:c>
-      <x:c r="B47" s="2" t="str">
+      <x:c r="B47" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C47" s="2" t="str">
+      <x:c r="C47" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D47" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E47" s="2"/>
+      <x:c r="D47" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E47" s="14"/>
     </x:row>
     <x:row r="48" ht="22" customHeight="1">
-      <x:c r="A48" s="2" t="str">
+      <x:c r="A48" s="14" t="str">
         <x:v>1 (126).docx</x:v>
       </x:c>
-      <x:c r="B48" s="2" t="str">
+      <x:c r="B48" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C48" s="2" t="str">
+      <x:c r="C48" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D48" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E48" s="2"/>
+      <x:c r="D48" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E48" s="14"/>
     </x:row>
     <x:row r="49" ht="22" customHeight="1">
-      <x:c r="A49" s="2" t="str">
+      <x:c r="A49" s="14" t="str">
         <x:v>1 (127).docx</x:v>
       </x:c>
-      <x:c r="B49" s="2" t="str">
+      <x:c r="B49" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C49" s="2" t="str">
+      <x:c r="C49" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D49" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E49" s="2"/>
+      <x:c r="D49" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E49" s="14"/>
     </x:row>
     <x:row r="50" ht="22" customHeight="1">
-      <x:c r="A50" s="2" t="str">
+      <x:c r="A50" s="14" t="str">
         <x:v>1 (128).docx</x:v>
       </x:c>
-      <x:c r="B50" s="2" t="str">
+      <x:c r="B50" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C50" s="2" t="str">
+      <x:c r="C50" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D50" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E50" s="2"/>
+      <x:c r="D50" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E50" s="14"/>
     </x:row>
     <x:row r="51" ht="22" customHeight="1">
-      <x:c r="A51" s="2" t="str">
+      <x:c r="A51" s="14" t="str">
         <x:v>1 (129).docx</x:v>
       </x:c>
-      <x:c r="B51" s="2" t="str">
+      <x:c r="B51" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C51" s="2" t="str">
+      <x:c r="C51" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D51" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E51" s="2"/>
+      <x:c r="D51" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E51" s="14"/>
     </x:row>
     <x:row r="52" ht="22" customHeight="1">
-      <x:c r="A52" s="2" t="str">
+      <x:c r="A52" s="14" t="str">
         <x:v>1 (13).docx</x:v>
       </x:c>
-      <x:c r="B52" s="2" t="str">
+      <x:c r="B52" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C52" s="2" t="str">
+      <x:c r="C52" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D52" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E52" s="2"/>
+      <x:c r="D52" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E52" s="14"/>
     </x:row>
     <x:row r="53" ht="22" customHeight="1">
-      <x:c r="A53" s="2" t="str">
+      <x:c r="A53" s="14" t="str">
         <x:v>1 (130).docx</x:v>
       </x:c>
-      <x:c r="B53" s="2" t="str">
+      <x:c r="B53" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C53" s="2" t="str">
+      <x:c r="C53" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D53" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E53" s="2"/>
+      <x:c r="D53" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E53" s="14"/>
     </x:row>
     <x:row r="54" ht="22" customHeight="1">
-      <x:c r="A54" s="2" t="str">
+      <x:c r="A54" s="14" t="str">
         <x:v>1 (131).docx</x:v>
       </x:c>
-      <x:c r="B54" s="2" t="str">
+      <x:c r="B54" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C54" s="2" t="str">
+      <x:c r="C54" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D54" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E54" s="2"/>
+      <x:c r="D54" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E54" s="14"/>
     </x:row>
     <x:row r="55" ht="22" customHeight="1">
-      <x:c r="A55" s="2" t="str">
+      <x:c r="A55" s="14" t="str">
         <x:v>1 (132).docx</x:v>
       </x:c>
-      <x:c r="B55" s="2" t="str">
+      <x:c r="B55" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C55" s="2" t="str">
+      <x:c r="C55" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D55" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E55" s="2"/>
+      <x:c r="D55" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E55" s="14"/>
     </x:row>
     <x:row r="56" ht="22" customHeight="1">
-      <x:c r="A56" s="2" t="str">
+      <x:c r="A56" s="14" t="str">
         <x:v>1 (133).docx</x:v>
       </x:c>
-      <x:c r="B56" s="2" t="str">
+      <x:c r="B56" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C56" s="2" t="str">
+      <x:c r="C56" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D56" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E56" s="2"/>
+      <x:c r="D56" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E56" s="14"/>
     </x:row>
     <x:row r="57" ht="22" customHeight="1">
-      <x:c r="A57" s="2" t="str">
+      <x:c r="A57" s="14" t="str">
         <x:v>1 (134).docx</x:v>
       </x:c>
-      <x:c r="B57" s="2" t="str">
+      <x:c r="B57" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C57" s="2" t="str">
+      <x:c r="C57" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D57" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E57" s="2"/>
+      <x:c r="D57" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E57" s="14"/>
     </x:row>
     <x:row r="58" ht="22" customHeight="1">
-      <x:c r="A58" s="2" t="str">
+      <x:c r="A58" s="14" t="str">
         <x:v>1 (135).docx</x:v>
       </x:c>
-      <x:c r="B58" s="2" t="str">
+      <x:c r="B58" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C58" s="2" t="str">
+      <x:c r="C58" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D58" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E58" s="2"/>
+      <x:c r="D58" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E58" s="14"/>
     </x:row>
     <x:row r="59" ht="22" customHeight="1">
-      <x:c r="A59" s="2" t="str">
+      <x:c r="A59" s="14" t="str">
         <x:v>1 (136).docx</x:v>
       </x:c>
-      <x:c r="B59" s="2" t="str">
+      <x:c r="B59" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C59" s="2" t="str">
+      <x:c r="C59" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D59" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E59" s="2"/>
+      <x:c r="D59" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E59" s="14"/>
     </x:row>
     <x:row r="60" ht="22" customHeight="1">
-      <x:c r="A60" s="2" t="str">
+      <x:c r="A60" s="14" t="str">
         <x:v>1 (137).docx</x:v>
       </x:c>
-      <x:c r="B60" s="2" t="str">
+      <x:c r="B60" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C60" s="2" t="str">
+      <x:c r="C60" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D60" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E60" s="2"/>
+      <x:c r="D60" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E60" s="14"/>
     </x:row>
     <x:row r="61" ht="22" customHeight="1">
-      <x:c r="A61" s="2" t="str">
+      <x:c r="A61" s="14" t="str">
         <x:v>1 (138).docx</x:v>
       </x:c>
-      <x:c r="B61" s="2" t="str">
+      <x:c r="B61" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C61" s="2" t="str">
+      <x:c r="C61" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D61" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E61" s="2"/>
+      <x:c r="D61" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E61" s="14"/>
     </x:row>
     <x:row r="62" ht="22" customHeight="1">
-      <x:c r="A62" s="2" t="str">
+      <x:c r="A62" s="14" t="str">
         <x:v>1 (139).docx</x:v>
       </x:c>
-      <x:c r="B62" s="2" t="str">
+      <x:c r="B62" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C62" s="2" t="str">
+      <x:c r="C62" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D62" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E62" s="2"/>
+      <x:c r="D62" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E62" s="14"/>
     </x:row>
     <x:row r="63" ht="22" customHeight="1">
-      <x:c r="A63" s="2" t="str">
+      <x:c r="A63" s="14" t="str">
         <x:v>1 (14).docx</x:v>
       </x:c>
-      <x:c r="B63" s="2" t="str">
+      <x:c r="B63" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C63" s="2" t="str">
+      <x:c r="C63" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D63" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E63" s="2"/>
+      <x:c r="D63" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E63" s="14"/>
     </x:row>
     <x:row r="64" ht="22" customHeight="1">
-      <x:c r="A64" s="2" t="str">
+      <x:c r="A64" s="14" t="str">
         <x:v>1 (140).docx</x:v>
       </x:c>
-      <x:c r="B64" s="2" t="str">
+      <x:c r="B64" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C64" s="2" t="str">
+      <x:c r="C64" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D64" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E64" s="2"/>
+      <x:c r="D64" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E64" s="14"/>
     </x:row>
     <x:row r="65" ht="22" customHeight="1">
-      <x:c r="A65" s="2" t="str">
+      <x:c r="A65" s="14" t="str">
         <x:v>1 (141).docx</x:v>
       </x:c>
-      <x:c r="B65" s="2" t="str">
+      <x:c r="B65" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C65" s="2" t="str">
+      <x:c r="C65" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D65" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E65" s="2"/>
+      <x:c r="D65" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E65" s="14"/>
     </x:row>
     <x:row r="66" ht="22" customHeight="1">
-      <x:c r="A66" s="2" t="str">
+      <x:c r="A66" s="14" t="str">
         <x:v>1 (142).docx</x:v>
       </x:c>
-      <x:c r="B66" s="2" t="str">
+      <x:c r="B66" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C66" s="2" t="str">
+      <x:c r="C66" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D66" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E66" s="2"/>
+      <x:c r="D66" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E66" s="14"/>
     </x:row>
     <x:row r="67" ht="22" customHeight="1">
-      <x:c r="A67" s="2" t="str">
+      <x:c r="A67" s="14" t="str">
         <x:v>1 (143).docx</x:v>
       </x:c>
-      <x:c r="B67" s="2" t="str">
+      <x:c r="B67" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C67" s="2" t="str">
+      <x:c r="C67" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D67" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E67" s="2"/>
+      <x:c r="D67" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E67" s="14"/>
     </x:row>
     <x:row r="68" ht="22" customHeight="1">
-      <x:c r="A68" s="2" t="str">
+      <x:c r="A68" s="14" t="str">
         <x:v>1 (144).docx</x:v>
       </x:c>
-      <x:c r="B68" s="2" t="str">
+      <x:c r="B68" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C68" s="2" t="str">
+      <x:c r="C68" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D68" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E68" s="2"/>
+      <x:c r="D68" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E68" s="14"/>
     </x:row>
     <x:row r="69" ht="22" customHeight="1">
-      <x:c r="A69" s="2" t="str">
+      <x:c r="A69" s="14" t="str">
         <x:v>1 (145).docx</x:v>
       </x:c>
-      <x:c r="B69" s="2" t="str">
+      <x:c r="B69" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C69" s="2" t="str">
+      <x:c r="C69" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D69" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E69" s="2"/>
+      <x:c r="D69" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E69" s="14"/>
     </x:row>
     <x:row r="70" ht="22" customHeight="1">
-      <x:c r="A70" s="2" t="str">
+      <x:c r="A70" s="14" t="str">
         <x:v>1 (146).docx</x:v>
       </x:c>
-      <x:c r="B70" s="2" t="str">
+      <x:c r="B70" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C70" s="2" t="str">
+      <x:c r="C70" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D70" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E70" s="2"/>
+      <x:c r="D70" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E70" s="14"/>
     </x:row>
     <x:row r="71" ht="22" customHeight="1">
-      <x:c r="A71" s="2" t="str">
+      <x:c r="A71" s="14" t="str">
         <x:v>1 (147).docx</x:v>
       </x:c>
-      <x:c r="B71" s="2" t="str">
+      <x:c r="B71" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C71" s="2" t="str">
+      <x:c r="C71" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D71" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E71" s="2"/>
+      <x:c r="D71" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E71" s="14"/>
     </x:row>
     <x:row r="72" ht="22" customHeight="1">
-      <x:c r="A72" s="2" t="str">
+      <x:c r="A72" s="14" t="str">
         <x:v>1 (148).docx</x:v>
       </x:c>
-      <x:c r="B72" s="2" t="str">
+      <x:c r="B72" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C72" s="2" t="str">
+      <x:c r="C72" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D72" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E72" s="2"/>
+      <x:c r="D72" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E72" s="14"/>
     </x:row>
     <x:row r="73" ht="22" customHeight="1">
-      <x:c r="A73" s="2" t="str">
+      <x:c r="A73" s="14" t="str">
         <x:v>1 (149).docx</x:v>
       </x:c>
-      <x:c r="B73" s="2" t="str">
+      <x:c r="B73" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C73" s="2" t="str">
+      <x:c r="C73" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D73" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E73" s="2"/>
+      <x:c r="D73" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E73" s="14"/>
     </x:row>
     <x:row r="74" ht="22" customHeight="1">
-      <x:c r="A74" s="2" t="str">
+      <x:c r="A74" s="14" t="str">
         <x:v>1 (15).docx</x:v>
       </x:c>
-      <x:c r="B74" s="2" t="str">
+      <x:c r="B74" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C74" s="2" t="str">
+      <x:c r="C74" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D74" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E74" s="2"/>
+      <x:c r="D74" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E74" s="14"/>
     </x:row>
     <x:row r="75" ht="22" customHeight="1">
-      <x:c r="A75" s="2" t="str">
+      <x:c r="A75" s="14" t="str">
         <x:v>1 (150).docx</x:v>
       </x:c>
-      <x:c r="B75" s="2" t="str">
+      <x:c r="B75" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C75" s="2" t="str">
+      <x:c r="C75" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D75" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E75" s="2"/>
+      <x:c r="D75" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E75" s="14"/>
     </x:row>
     <x:row r="76" ht="22" customHeight="1">
-      <x:c r="A76" s="2" t="str">
+      <x:c r="A76" s="14" t="str">
         <x:v>1 (151).docx</x:v>
       </x:c>
-      <x:c r="B76" s="2" t="str">
+      <x:c r="B76" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C76" s="2" t="str">
+      <x:c r="C76" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D76" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E76" s="2"/>
+      <x:c r="D76" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E76" s="14"/>
     </x:row>
     <x:row r="77" ht="22" customHeight="1">
-      <x:c r="A77" s="2" t="str">
+      <x:c r="A77" s="14" t="str">
         <x:v>1 (152).docx</x:v>
       </x:c>
-      <x:c r="B77" s="2" t="str">
+      <x:c r="B77" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C77" s="2" t="str">
+      <x:c r="C77" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D77" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E77" s="2"/>
+      <x:c r="D77" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E77" s="14"/>
     </x:row>
     <x:row r="78" ht="22" customHeight="1">
-      <x:c r="A78" s="2" t="str">
+      <x:c r="A78" s="14" t="str">
         <x:v>1 (153).docx</x:v>
       </x:c>
-      <x:c r="B78" s="2" t="str">
+      <x:c r="B78" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C78" s="2" t="str">
+      <x:c r="C78" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D78" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E78" s="2"/>
+      <x:c r="D78" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E78" s="14"/>
     </x:row>
     <x:row r="79" ht="22" customHeight="1">
-      <x:c r="A79" s="2" t="str">
+      <x:c r="A79" s="14" t="str">
         <x:v>1 (154).docx</x:v>
       </x:c>
-      <x:c r="B79" s="2" t="str">
+      <x:c r="B79" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C79" s="2" t="str">
+      <x:c r="C79" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D79" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E79" s="2"/>
+      <x:c r="D79" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E79" s="14"/>
     </x:row>
     <x:row r="80" ht="22" customHeight="1">
-      <x:c r="A80" s="2" t="str">
+      <x:c r="A80" s="14" t="str">
         <x:v>1 (155).docx</x:v>
       </x:c>
-      <x:c r="B80" s="2" t="str">
+      <x:c r="B80" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C80" s="2" t="str">
+      <x:c r="C80" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D80" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E80" s="2"/>
+      <x:c r="D80" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E80" s="14"/>
     </x:row>
     <x:row r="81" ht="22" customHeight="1">
-      <x:c r="A81" s="2" t="str">
+      <x:c r="A81" s="14" t="str">
         <x:v>1 (156).docx</x:v>
       </x:c>
-      <x:c r="B81" s="2" t="str">
+      <x:c r="B81" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C81" s="2" t="str">
+      <x:c r="C81" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D81" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E81" s="2"/>
+      <x:c r="D81" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E81" s="14"/>
     </x:row>
     <x:row r="82" ht="22" customHeight="1">
-      <x:c r="A82" s="2" t="str">
+      <x:c r="A82" s="14" t="str">
         <x:v>1 (157).docx</x:v>
       </x:c>
-      <x:c r="B82" s="2" t="str">
+      <x:c r="B82" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C82" s="2" t="str">
+      <x:c r="C82" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D82" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E82" s="2"/>
+      <x:c r="D82" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E82" s="14"/>
     </x:row>
     <x:row r="83" ht="22" customHeight="1">
-      <x:c r="A83" s="2" t="str">
+      <x:c r="A83" s="14" t="str">
         <x:v>1 (158).docx</x:v>
       </x:c>
-      <x:c r="B83" s="2" t="str">
+      <x:c r="B83" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C83" s="2" t="str">
+      <x:c r="C83" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D83" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E83" s="2"/>
+      <x:c r="D83" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E83" s="14"/>
     </x:row>
     <x:row r="84" ht="22" customHeight="1">
-      <x:c r="A84" s="2" t="str">
+      <x:c r="A84" s="14" t="str">
         <x:v>1 (159).docx</x:v>
       </x:c>
-      <x:c r="B84" s="2" t="str">
+      <x:c r="B84" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C84" s="2" t="str">
+      <x:c r="C84" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D84" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E84" s="2"/>
+      <x:c r="D84" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E84" s="14"/>
     </x:row>
     <x:row r="85" ht="22" customHeight="1">
-      <x:c r="A85" s="2" t="str">
+      <x:c r="A85" s="14" t="str">
         <x:v>1 (16).docx</x:v>
       </x:c>
-      <x:c r="B85" s="2" t="str">
+      <x:c r="B85" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C85" s="2" t="str">
+      <x:c r="C85" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D85" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E85" s="2"/>
+      <x:c r="D85" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E85" s="14"/>
     </x:row>
     <x:row r="86" ht="22" customHeight="1">
-      <x:c r="A86" s="2" t="str">
+      <x:c r="A86" s="14" t="str">
         <x:v>1 (160).docx</x:v>
       </x:c>
-      <x:c r="B86" s="2" t="str">
+      <x:c r="B86" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C86" s="2" t="str">
+      <x:c r="C86" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D86" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E86" s="2"/>
+      <x:c r="D86" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E86" s="14"/>
     </x:row>
     <x:row r="87" ht="22" customHeight="1">
-      <x:c r="A87" s="2" t="str">
+      <x:c r="A87" s="14" t="str">
         <x:v>1 (161).docx</x:v>
       </x:c>
-      <x:c r="B87" s="2" t="str">
+      <x:c r="B87" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C87" s="2" t="str">
+      <x:c r="C87" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D87" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E87" s="2"/>
+      <x:c r="D87" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E87" s="14"/>
     </x:row>
     <x:row r="88" ht="22" customHeight="1">
-      <x:c r="A88" s="2" t="str">
+      <x:c r="A88" s="14" t="str">
         <x:v>1 (162).docx</x:v>
       </x:c>
-      <x:c r="B88" s="2" t="str">
+      <x:c r="B88" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C88" s="2" t="str">
+      <x:c r="C88" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D88" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E88" s="2"/>
+      <x:c r="D88" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E88" s="14"/>
     </x:row>
     <x:row r="89" ht="22" customHeight="1">
-      <x:c r="A89" s="2" t="str">
+      <x:c r="A89" s="14" t="str">
         <x:v>1 (163).docx</x:v>
       </x:c>
-      <x:c r="B89" s="2" t="str">
+      <x:c r="B89" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C89" s="2" t="str">
+      <x:c r="C89" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D89" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E89" s="2"/>
+      <x:c r="D89" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E89" s="14"/>
     </x:row>
     <x:row r="90" ht="22" customHeight="1">
-      <x:c r="A90" s="2" t="str">
+      <x:c r="A90" s="14" t="str">
         <x:v>1 (164).docx</x:v>
       </x:c>
-      <x:c r="B90" s="2" t="str">
+      <x:c r="B90" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C90" s="2" t="str">
+      <x:c r="C90" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D90" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E90" s="2"/>
+      <x:c r="D90" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E90" s="14"/>
     </x:row>
     <x:row r="91" ht="22" customHeight="1">
-      <x:c r="A91" s="2" t="str">
+      <x:c r="A91" s="14" t="str">
         <x:v>1 (165).docx</x:v>
       </x:c>
-      <x:c r="B91" s="2" t="str">
+      <x:c r="B91" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C91" s="2" t="str">
+      <x:c r="C91" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D91" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E91" s="2"/>
+      <x:c r="D91" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E91" s="14"/>
     </x:row>
     <x:row r="92" ht="22" customHeight="1">
-      <x:c r="A92" s="2" t="str">
+      <x:c r="A92" s="14" t="str">
         <x:v>1 (166).docx</x:v>
       </x:c>
-      <x:c r="B92" s="2" t="str">
+      <x:c r="B92" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C92" s="2" t="str">
+      <x:c r="C92" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D92" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E92" s="2"/>
+      <x:c r="D92" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E92" s="14"/>
     </x:row>
     <x:row r="93" ht="22" customHeight="1">
-      <x:c r="A93" s="2" t="str">
+      <x:c r="A93" s="14" t="str">
         <x:v>1 (167).docx</x:v>
       </x:c>
-      <x:c r="B93" s="2" t="str">
+      <x:c r="B93" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C93" s="2" t="str">
+      <x:c r="C93" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D93" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E93" s="2"/>
+      <x:c r="D93" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E93" s="14"/>
     </x:row>
     <x:row r="94" ht="22" customHeight="1">
-      <x:c r="A94" s="2" t="str">
+      <x:c r="A94" s="14" t="str">
         <x:v>1 (168).docx</x:v>
       </x:c>
-      <x:c r="B94" s="2" t="str">
+      <x:c r="B94" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C94" s="2" t="str">
+      <x:c r="C94" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D94" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E94" s="2"/>
+      <x:c r="D94" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E94" s="14"/>
     </x:row>
     <x:row r="95" ht="22" customHeight="1">
-      <x:c r="A95" s="2" t="str">
+      <x:c r="A95" s="14" t="str">
         <x:v>1 (169).docx</x:v>
       </x:c>
-      <x:c r="B95" s="2" t="str">
+      <x:c r="B95" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C95" s="2" t="str">
+      <x:c r="C95" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D95" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E95" s="2"/>
+      <x:c r="D95" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E95" s="14"/>
     </x:row>
     <x:row r="96" ht="22" customHeight="1">
-      <x:c r="A96" s="2" t="str">
+      <x:c r="A96" s="14" t="str">
         <x:v>1 (17).docx</x:v>
       </x:c>
-      <x:c r="B96" s="2" t="str">
+      <x:c r="B96" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C96" s="2" t="str">
+      <x:c r="C96" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D96" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E96" s="2"/>
+      <x:c r="D96" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E96" s="14"/>
     </x:row>
     <x:row r="97" ht="22" customHeight="1">
-      <x:c r="A97" s="2" t="str">
+      <x:c r="A97" s="14" t="str">
         <x:v>1 (170).docx</x:v>
       </x:c>
-      <x:c r="B97" s="2" t="str">
+      <x:c r="B97" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C97" s="2" t="str">
+      <x:c r="C97" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D97" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E97" s="2"/>
+      <x:c r="D97" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E97" s="14"/>
     </x:row>
     <x:row r="98" ht="22" customHeight="1">
-      <x:c r="A98" s="2" t="str">
+      <x:c r="A98" s="14" t="str">
         <x:v>1 (171).docx</x:v>
       </x:c>
-      <x:c r="B98" s="2" t="str">
+      <x:c r="B98" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C98" s="2" t="str">
+      <x:c r="C98" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D98" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E98" s="2"/>
+      <x:c r="D98" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E98" s="14"/>
     </x:row>
     <x:row r="99" ht="22" customHeight="1">
-      <x:c r="A99" s="2" t="str">
+      <x:c r="A99" s="14" t="str">
         <x:v>1 (172).docx</x:v>
       </x:c>
-      <x:c r="B99" s="2" t="str">
+      <x:c r="B99" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C99" s="2" t="str">
+      <x:c r="C99" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D99" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E99" s="2"/>
+      <x:c r="D99" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E99" s="14"/>
     </x:row>
     <x:row r="100" ht="22" customHeight="1">
-      <x:c r="A100" s="2" t="str">
+      <x:c r="A100" s="14" t="str">
         <x:v>1 (173).docx</x:v>
       </x:c>
-      <x:c r="B100" s="2" t="str">
+      <x:c r="B100" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C100" s="2" t="str">
+      <x:c r="C100" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D100" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E100" s="2"/>
+      <x:c r="D100" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E100" s="14"/>
     </x:row>
     <x:row r="101" ht="22" customHeight="1">
-      <x:c r="A101" s="2" t="str">
+      <x:c r="A101" s="14" t="str">
         <x:v>1 (174).docx</x:v>
       </x:c>
-      <x:c r="B101" s="2" t="str">
+      <x:c r="B101" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C101" s="2" t="str">
+      <x:c r="C101" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D101" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E101" s="2"/>
+      <x:c r="D101" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E101" s="14"/>
     </x:row>
     <x:row r="102" ht="22" customHeight="1">
-      <x:c r="A102" s="2" t="str">
+      <x:c r="A102" s="14" t="str">
         <x:v>1 (175).docx</x:v>
       </x:c>
-      <x:c r="B102" s="2" t="str">
+      <x:c r="B102" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C102" s="2" t="str">
+      <x:c r="C102" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D102" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E102" s="2"/>
+      <x:c r="D102" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E102" s="14"/>
     </x:row>
     <x:row r="103" ht="22" customHeight="1">
-      <x:c r="A103" s="2" t="str">
+      <x:c r="A103" s="14" t="str">
         <x:v>1 (176).docx</x:v>
       </x:c>
-      <x:c r="B103" s="2" t="str">
+      <x:c r="B103" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C103" s="2" t="str">
+      <x:c r="C103" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D103" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E103" s="2"/>
+      <x:c r="D103" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E103" s="14"/>
     </x:row>
     <x:row r="104" ht="22" customHeight="1">
-      <x:c r="A104" s="2" t="str">
+      <x:c r="A104" s="14" t="str">
         <x:v>1 (177).docx</x:v>
       </x:c>
-      <x:c r="B104" s="2" t="str">
+      <x:c r="B104" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C104" s="2" t="str">
+      <x:c r="C104" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D104" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E104" s="2"/>
+      <x:c r="D104" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E104" s="14"/>
     </x:row>
     <x:row r="105" ht="22" customHeight="1">
-      <x:c r="A105" s="2" t="str">
+      <x:c r="A105" s="14" t="str">
         <x:v>1 (178).docx</x:v>
       </x:c>
-      <x:c r="B105" s="2" t="str">
+      <x:c r="B105" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C105" s="2" t="str">
+      <x:c r="C105" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D105" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E105" s="2"/>
+      <x:c r="D105" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E105" s="14"/>
     </x:row>
     <x:row r="106" ht="22" customHeight="1">
-      <x:c r="A106" s="2" t="str">
+      <x:c r="A106" s="14" t="str">
         <x:v>1 (179).docx</x:v>
       </x:c>
-      <x:c r="B106" s="2" t="str">
+      <x:c r="B106" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C106" s="2" t="str">
+      <x:c r="C106" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D106" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E106" s="2"/>
+      <x:c r="D106" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E106" s="14"/>
     </x:row>
     <x:row r="107" ht="22" customHeight="1">
-      <x:c r="A107" s="2" t="str">
+      <x:c r="A107" s="14" t="str">
         <x:v>1 (18).docx</x:v>
       </x:c>
-      <x:c r="B107" s="2" t="str">
+      <x:c r="B107" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C107" s="2" t="str">
+      <x:c r="C107" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D107" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E107" s="2"/>
+      <x:c r="D107" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E107" s="14"/>
     </x:row>
     <x:row r="108" ht="22" customHeight="1">
-      <x:c r="A108" s="2" t="str">
+      <x:c r="A108" s="14" t="str">
         <x:v>1 (180).docx</x:v>
       </x:c>
-      <x:c r="B108" s="2" t="str">
+      <x:c r="B108" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C108" s="2" t="str">
+      <x:c r="C108" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D108" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E108" s="2"/>
+      <x:c r="D108" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E108" s="14"/>
     </x:row>
     <x:row r="109" ht="22" customHeight="1">
-      <x:c r="A109" s="2" t="str">
+      <x:c r="A109" s="14" t="str">
         <x:v>1 (181).docx</x:v>
       </x:c>
-      <x:c r="B109" s="2" t="str">
+      <x:c r="B109" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C109" s="2" t="str">
+      <x:c r="C109" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D109" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E109" s="2"/>
+      <x:c r="D109" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E109" s="14"/>
     </x:row>
     <x:row r="110" ht="22" customHeight="1">
-      <x:c r="A110" s="2" t="str">
+      <x:c r="A110" s="14" t="str">
         <x:v>1 (182).docx</x:v>
       </x:c>
-      <x:c r="B110" s="2" t="str">
+      <x:c r="B110" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C110" s="2" t="str">
+      <x:c r="C110" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D110" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E110" s="2"/>
+      <x:c r="D110" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E110" s="14"/>
     </x:row>
     <x:row r="111" ht="22" customHeight="1">
-      <x:c r="A111" s="2" t="str">
+      <x:c r="A111" s="14" t="str">
         <x:v>1 (183).docx</x:v>
       </x:c>
-      <x:c r="B111" s="2" t="str">
+      <x:c r="B111" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C111" s="2" t="str">
+      <x:c r="C111" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D111" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E111" s="2"/>
+      <x:c r="D111" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E111" s="14"/>
     </x:row>
     <x:row r="112" ht="22" customHeight="1">
-      <x:c r="A112" s="2" t="str">
+      <x:c r="A112" s="14" t="str">
         <x:v>1 (184).docx</x:v>
       </x:c>
-      <x:c r="B112" s="2" t="str">
+      <x:c r="B112" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C112" s="2" t="str">
+      <x:c r="C112" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D112" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E112" s="2"/>
+      <x:c r="D112" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E112" s="14"/>
     </x:row>
     <x:row r="113" ht="22" customHeight="1">
-      <x:c r="A113" s="2" t="str">
+      <x:c r="A113" s="14" t="str">
         <x:v>1 (185).docx</x:v>
       </x:c>
-      <x:c r="B113" s="2" t="str">
+      <x:c r="B113" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C113" s="2" t="str">
+      <x:c r="C113" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D113" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E113" s="2"/>
+      <x:c r="D113" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E113" s="14"/>
     </x:row>
     <x:row r="114" ht="22" customHeight="1">
-      <x:c r="A114" s="2" t="str">
+      <x:c r="A114" s="14" t="str">
         <x:v>1 (186).docx</x:v>
       </x:c>
-      <x:c r="B114" s="2" t="str">
+      <x:c r="B114" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C114" s="2" t="str">
+      <x:c r="C114" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D114" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E114" s="2"/>
+      <x:c r="D114" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E114" s="14"/>
     </x:row>
     <x:row r="115" ht="22" customHeight="1">
-      <x:c r="A115" s="2" t="str">
+      <x:c r="A115" s="14" t="str">
         <x:v>1 (187).docx</x:v>
       </x:c>
-      <x:c r="B115" s="2" t="str">
+      <x:c r="B115" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C115" s="2" t="str">
+      <x:c r="C115" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D115" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E115" s="2"/>
+      <x:c r="D115" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E115" s="14"/>
     </x:row>
     <x:row r="116" ht="22" customHeight="1">
-      <x:c r="A116" s="2" t="str">
+      <x:c r="A116" s="14" t="str">
         <x:v>1 (188).docx</x:v>
       </x:c>
-      <x:c r="B116" s="2" t="str">
+      <x:c r="B116" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C116" s="2" t="str">
+      <x:c r="C116" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D116" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E116" s="2"/>
+      <x:c r="D116" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E116" s="14"/>
     </x:row>
     <x:row r="117" ht="22" customHeight="1">
-      <x:c r="A117" s="2" t="str">
+      <x:c r="A117" s="14" t="str">
         <x:v>1 (189).docx</x:v>
       </x:c>
-      <x:c r="B117" s="2" t="str">
+      <x:c r="B117" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C117" s="2" t="str">
+      <x:c r="C117" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D117" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E117" s="2"/>
+      <x:c r="D117" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E117" s="14"/>
     </x:row>
     <x:row r="118" ht="22" customHeight="1">
-      <x:c r="A118" s="2" t="str">
+      <x:c r="A118" s="14" t="str">
         <x:v>1 (19).docx</x:v>
       </x:c>
-      <x:c r="B118" s="2" t="str">
+      <x:c r="B118" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C118" s="2" t="str">
+      <x:c r="C118" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D118" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E118" s="2"/>
+      <x:c r="D118" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E118" s="14"/>
     </x:row>
     <x:row r="119" ht="22" customHeight="1">
-      <x:c r="A119" s="2" t="str">
+      <x:c r="A119" s="14" t="str">
         <x:v>1 (190).docx</x:v>
       </x:c>
-      <x:c r="B119" s="2" t="str">
+      <x:c r="B119" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C119" s="2" t="str">
+      <x:c r="C119" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D119" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E119" s="2"/>
+      <x:c r="D119" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E119" s="14"/>
     </x:row>
     <x:row r="120" ht="22" customHeight="1">
-      <x:c r="A120" s="2" t="str">
+      <x:c r="A120" s="14" t="str">
         <x:v>1 (191).docx</x:v>
       </x:c>
-      <x:c r="B120" s="2" t="str">
+      <x:c r="B120" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C120" s="2" t="str">
+      <x:c r="C120" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D120" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E120" s="2"/>
+      <x:c r="D120" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E120" s="14"/>
     </x:row>
     <x:row r="121" ht="22" customHeight="1">
-      <x:c r="A121" s="2" t="str">
+      <x:c r="A121" s="14" t="str">
         <x:v>1 (192).docx</x:v>
       </x:c>
-      <x:c r="B121" s="2" t="str">
+      <x:c r="B121" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C121" s="2" t="str">
+      <x:c r="C121" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D121" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E121" s="2"/>
+      <x:c r="D121" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E121" s="14"/>
     </x:row>
     <x:row r="122" ht="22" customHeight="1">
-      <x:c r="A122" s="2" t="str">
+      <x:c r="A122" s="14" t="str">
         <x:v>1 (193).docx</x:v>
       </x:c>
-      <x:c r="B122" s="2" t="str">
+      <x:c r="B122" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C122" s="2" t="str">
+      <x:c r="C122" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D122" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E122" s="2"/>
+      <x:c r="D122" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E122" s="14"/>
     </x:row>
     <x:row r="123" ht="22" customHeight="1">
-      <x:c r="A123" s="2" t="str">
+      <x:c r="A123" s="14" t="str">
         <x:v>1 (194).docx</x:v>
       </x:c>
-      <x:c r="B123" s="2" t="str">
+      <x:c r="B123" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C123" s="2" t="str">
+      <x:c r="C123" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D123" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E123" s="2"/>
+      <x:c r="D123" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E123" s="14"/>
     </x:row>
     <x:row r="124" ht="22" customHeight="1">
-      <x:c r="A124" s="2" t="str">
+      <x:c r="A124" s="14" t="str">
         <x:v>1 (195).docx</x:v>
       </x:c>
-      <x:c r="B124" s="2" t="str">
+      <x:c r="B124" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C124" s="2" t="str">
+      <x:c r="C124" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D124" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E124" s="2"/>
+      <x:c r="D124" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E124" s="14"/>
     </x:row>
     <x:row r="125" ht="22" customHeight="1">
-      <x:c r="A125" s="2" t="str">
+      <x:c r="A125" s="14" t="str">
         <x:v>1 (197).docx</x:v>
       </x:c>
-      <x:c r="B125" s="2" t="str">
+      <x:c r="B125" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C125" s="2" t="str">
+      <x:c r="C125" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D125" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E125" s="2"/>
+      <x:c r="D125" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E125" s="14"/>
     </x:row>
     <x:row r="126" ht="22" customHeight="1">
-      <x:c r="A126" s="2" t="str">
+      <x:c r="A126" s="14" t="str">
         <x:v>1 (198).docx</x:v>
       </x:c>
-      <x:c r="B126" s="2" t="str">
+      <x:c r="B126" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C126" s="2" t="str">
+      <x:c r="C126" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D126" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E126" s="2"/>
+      <x:c r="D126" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E126" s="14"/>
     </x:row>
     <x:row r="127" ht="22" customHeight="1">
-      <x:c r="A127" s="2" t="str">
+      <x:c r="A127" s="14" t="str">
         <x:v>1 (199).docx</x:v>
       </x:c>
-      <x:c r="B127" s="2" t="str">
+      <x:c r="B127" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C127" s="2" t="str">
+      <x:c r="C127" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D127" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E127" s="2"/>
+      <x:c r="D127" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E127" s="14"/>
     </x:row>
     <x:row r="128" ht="22" customHeight="1">
-      <x:c r="A128" s="2" t="str">
+      <x:c r="A128" s="14" t="str">
         <x:v>1 (2).docx</x:v>
       </x:c>
-      <x:c r="B128" s="2" t="str">
+      <x:c r="B128" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C128" s="2" t="str">
+      <x:c r="C128" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D128" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E128" s="2"/>
+      <x:c r="D128" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E128" s="14"/>
     </x:row>
     <x:row r="129" ht="22" customHeight="1">
-      <x:c r="A129" s="2" t="str">
+      <x:c r="A129" s="14" t="str">
         <x:v>1 (20).docx</x:v>
       </x:c>
-      <x:c r="B129" s="2" t="str">
+      <x:c r="B129" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C129" s="2" t="str">
+      <x:c r="C129" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D129" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E129" s="2"/>
+      <x:c r="D129" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E129" s="14"/>
     </x:row>
     <x:row r="130" ht="22" customHeight="1">
-      <x:c r="A130" s="2" t="str">
+      <x:c r="A130" s="14" t="str">
         <x:v>1 (200).docx</x:v>
       </x:c>
-      <x:c r="B130" s="2" t="str">
+      <x:c r="B130" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C130" s="2" t="str">
+      <x:c r="C130" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D130" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E130" s="2"/>
+      <x:c r="D130" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E130" s="14"/>
     </x:row>
     <x:row r="131" ht="22" customHeight="1">
-      <x:c r="A131" s="2" t="str">
+      <x:c r="A131" s="14" t="str">
         <x:v>1 (201).docx</x:v>
       </x:c>
-      <x:c r="B131" s="2" t="str">
+      <x:c r="B131" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C131" s="2" t="str">
+      <x:c r="C131" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D131" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E131" s="2"/>
+      <x:c r="D131" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E131" s="14"/>
     </x:row>
     <x:row r="132" ht="22" customHeight="1">
-      <x:c r="A132" s="2" t="str">
+      <x:c r="A132" s="14" t="str">
         <x:v>1 (202).docx</x:v>
       </x:c>
-      <x:c r="B132" s="2" t="str">
+      <x:c r="B132" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C132" s="2" t="str">
+      <x:c r="C132" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D132" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E132" s="2"/>
+      <x:c r="D132" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E132" s="14"/>
     </x:row>
     <x:row r="133" ht="22" customHeight="1">
-      <x:c r="A133" s="2" t="str">
+      <x:c r="A133" s="14" t="str">
         <x:v>1 (203).docx</x:v>
       </x:c>
-      <x:c r="B133" s="2" t="str">
+      <x:c r="B133" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C133" s="2" t="str">
+      <x:c r="C133" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D133" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E133" s="2"/>
+      <x:c r="D133" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E133" s="14"/>
     </x:row>
     <x:row r="134" ht="22" customHeight="1">
-      <x:c r="A134" s="2" t="str">
+      <x:c r="A134" s="14" t="str">
         <x:v>1 (21).docx</x:v>
       </x:c>
-      <x:c r="B134" s="2" t="str">
+      <x:c r="B134" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C134" s="2" t="str">
+      <x:c r="C134" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D134" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E134" s="2"/>
+      <x:c r="D134" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E134" s="14"/>
     </x:row>
     <x:row r="135" ht="22" customHeight="1">
-      <x:c r="A135" s="2" t="str">
+      <x:c r="A135" s="14" t="str">
         <x:v>1 (22).docx</x:v>
       </x:c>
-      <x:c r="B135" s="2" t="str">
+      <x:c r="B135" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C135" s="2" t="str">
+      <x:c r="C135" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D135" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E135" s="2"/>
+      <x:c r="D135" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E135" s="14"/>
     </x:row>
     <x:row r="136" ht="22" customHeight="1">
-      <x:c r="A136" s="2" t="str">
+      <x:c r="A136" s="14" t="str">
         <x:v>1 (23).docx</x:v>
       </x:c>
-      <x:c r="B136" s="2" t="str">
+      <x:c r="B136" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C136" s="2" t="str">
+      <x:c r="C136" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D136" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E136" s="2"/>
+      <x:c r="D136" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E136" s="14"/>
     </x:row>
     <x:row r="137" ht="22" customHeight="1">
-      <x:c r="A137" s="2" t="str">
+      <x:c r="A137" s="14" t="str">
         <x:v>1 (24).docx</x:v>
       </x:c>
-      <x:c r="B137" s="2" t="str">
+      <x:c r="B137" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C137" s="2" t="str">
+      <x:c r="C137" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D137" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E137" s="2"/>
+      <x:c r="D137" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E137" s="14"/>
     </x:row>
     <x:row r="138" ht="22" customHeight="1">
-      <x:c r="A138" s="2" t="str">
+      <x:c r="A138" s="14" t="str">
         <x:v>1 (25).docx</x:v>
       </x:c>
-      <x:c r="B138" s="2" t="str">
+      <x:c r="B138" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C138" s="2" t="str">
+      <x:c r="C138" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D138" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E138" s="2"/>
+      <x:c r="D138" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E138" s="14"/>
     </x:row>
     <x:row r="139" ht="22" customHeight="1">
-      <x:c r="A139" s="2" t="str">
+      <x:c r="A139" s="14" t="str">
         <x:v>1 (26).docx</x:v>
       </x:c>
-      <x:c r="B139" s="2" t="str">
+      <x:c r="B139" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C139" s="2" t="str">
+      <x:c r="C139" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D139" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E139" s="2"/>
+      <x:c r="D139" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E139" s="14"/>
     </x:row>
     <x:row r="140" ht="22" customHeight="1">
-      <x:c r="A140" s="2" t="str">
+      <x:c r="A140" s="14" t="str">
         <x:v>1 (27).docx</x:v>
       </x:c>
-      <x:c r="B140" s="2" t="str">
+      <x:c r="B140" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C140" s="2" t="str">
+      <x:c r="C140" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D140" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E140" s="2"/>
+      <x:c r="D140" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E140" s="14"/>
     </x:row>
     <x:row r="141" ht="22" customHeight="1">
-      <x:c r="A141" s="2" t="str">
+      <x:c r="A141" s="14" t="str">
         <x:v>1 (28).docx</x:v>
       </x:c>
-      <x:c r="B141" s="2" t="str">
+      <x:c r="B141" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C141" s="2" t="str">
+      <x:c r="C141" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D141" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E141" s="2"/>
+      <x:c r="D141" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E141" s="14"/>
     </x:row>
     <x:row r="142" ht="22" customHeight="1">
-      <x:c r="A142" s="2" t="str">
+      <x:c r="A142" s="14" t="str">
         <x:v>1 (29).docx</x:v>
       </x:c>
-      <x:c r="B142" s="2" t="str">
+      <x:c r="B142" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C142" s="2" t="str">
+      <x:c r="C142" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D142" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E142" s="2"/>
+      <x:c r="D142" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E142" s="14"/>
     </x:row>
     <x:row r="143" ht="22" customHeight="1">
-      <x:c r="A143" s="2" t="str">
+      <x:c r="A143" s="14" t="str">
         <x:v>1 (3).docx</x:v>
       </x:c>
-      <x:c r="B143" s="2" t="str">
+      <x:c r="B143" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C143" s="2" t="str">
+      <x:c r="C143" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D143" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E143" s="2"/>
+      <x:c r="D143" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E143" s="14"/>
     </x:row>
     <x:row r="144" ht="22" customHeight="1">
-      <x:c r="A144" s="2" t="str">
+      <x:c r="A144" s="14" t="str">
         <x:v>1 (30).docx</x:v>
       </x:c>
-      <x:c r="B144" s="2" t="str">
+      <x:c r="B144" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C144" s="2" t="str">
+      <x:c r="C144" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D144" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E144" s="2"/>
+      <x:c r="D144" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E144" s="14"/>
     </x:row>
     <x:row r="145" ht="22" customHeight="1">
-      <x:c r="A145" s="2" t="str">
+      <x:c r="A145" s="14" t="str">
         <x:v>1 (31).docx</x:v>
       </x:c>
-      <x:c r="B145" s="2" t="str">
+      <x:c r="B145" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C145" s="2" t="str">
+      <x:c r="C145" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D145" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E145" s="2"/>
+      <x:c r="D145" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E145" s="14"/>
     </x:row>
     <x:row r="146" ht="22" customHeight="1">
-      <x:c r="A146" s="2" t="str">
+      <x:c r="A146" s="14" t="str">
         <x:v>1 (32).docx</x:v>
       </x:c>
-      <x:c r="B146" s="2" t="str">
+      <x:c r="B146" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C146" s="2" t="str">
+      <x:c r="C146" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D146" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E146" s="2"/>
+      <x:c r="D146" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E146" s="14"/>
     </x:row>
     <x:row r="147" ht="22" customHeight="1">
-      <x:c r="A147" s="2" t="str">
+      <x:c r="A147" s="14" t="str">
         <x:v>1 (33).docx</x:v>
       </x:c>
-      <x:c r="B147" s="2" t="str">
+      <x:c r="B147" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C147" s="2" t="str">
+      <x:c r="C147" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D147" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E147" s="2"/>
+      <x:c r="D147" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E147" s="14"/>
     </x:row>
     <x:row r="148" ht="22" customHeight="1">
-      <x:c r="A148" s="2" t="str">
+      <x:c r="A148" s="14" t="str">
         <x:v>1 (34).docx</x:v>
       </x:c>
-      <x:c r="B148" s="2" t="str">
+      <x:c r="B148" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C148" s="2" t="str">
+      <x:c r="C148" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D148" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E148" s="2"/>
+      <x:c r="D148" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E148" s="14"/>
     </x:row>
     <x:row r="149" ht="22" customHeight="1">
-      <x:c r="A149" s="2" t="str">
+      <x:c r="A149" s="14" t="str">
         <x:v>1 (35).docx</x:v>
       </x:c>
-      <x:c r="B149" s="2" t="str">
+      <x:c r="B149" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C149" s="2" t="str">
+      <x:c r="C149" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D149" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E149" s="2"/>
+      <x:c r="D149" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E149" s="14"/>
     </x:row>
     <x:row r="150" ht="22" customHeight="1">
-      <x:c r="A150" s="2" t="str">
+      <x:c r="A150" s="14" t="str">
         <x:v>1 (36).docx</x:v>
       </x:c>
-      <x:c r="B150" s="2" t="str">
+      <x:c r="B150" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C150" s="2" t="str">
+      <x:c r="C150" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D150" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E150" s="2"/>
+      <x:c r="D150" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E150" s="14"/>
     </x:row>
     <x:row r="151" ht="22" customHeight="1">
-      <x:c r="A151" s="2" t="str">
+      <x:c r="A151" s="14" t="str">
         <x:v>1 (37).docx</x:v>
       </x:c>
-      <x:c r="B151" s="2" t="str">
+      <x:c r="B151" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C151" s="2" t="str">
+      <x:c r="C151" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D151" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E151" s="2"/>
+      <x:c r="D151" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E151" s="14"/>
     </x:row>
     <x:row r="152" ht="22" customHeight="1">
-      <x:c r="A152" s="2" t="str">
+      <x:c r="A152" s="14" t="str">
         <x:v>1 (38).docx</x:v>
       </x:c>
-      <x:c r="B152" s="2" t="str">
+      <x:c r="B152" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C152" s="2" t="str">
+      <x:c r="C152" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D152" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E152" s="2"/>
+      <x:c r="D152" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E152" s="14"/>
     </x:row>
     <x:row r="153" ht="22" customHeight="1">
-      <x:c r="A153" s="2" t="str">
+      <x:c r="A153" s="14" t="str">
         <x:v>1 (39).docx</x:v>
       </x:c>
-      <x:c r="B153" s="2" t="str">
+      <x:c r="B153" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C153" s="2" t="str">
+      <x:c r="C153" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D153" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E153" s="2"/>
+      <x:c r="D153" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E153" s="14"/>
     </x:row>
     <x:row r="154" ht="22" customHeight="1">
-      <x:c r="A154" s="2" t="str">
+      <x:c r="A154" s="14" t="str">
         <x:v>1 (4).docx</x:v>
       </x:c>
-      <x:c r="B154" s="2" t="str">
+      <x:c r="B154" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C154" s="2" t="str">
+      <x:c r="C154" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D154" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E154" s="2"/>
+      <x:c r="D154" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E154" s="14"/>
     </x:row>
     <x:row r="155" ht="22" customHeight="1">
-      <x:c r="A155" s="2" t="str">
+      <x:c r="A155" s="14" t="str">
         <x:v>1 (40).docx</x:v>
       </x:c>
-      <x:c r="B155" s="2" t="str">
+      <x:c r="B155" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C155" s="2" t="str">
+      <x:c r="C155" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D155" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E155" s="2"/>
+      <x:c r="D155" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E155" s="14"/>
     </x:row>
     <x:row r="156" ht="22" customHeight="1">
-      <x:c r="A156" s="2" t="str">
+      <x:c r="A156" s="14" t="str">
         <x:v>1 (41).docx</x:v>
       </x:c>
-      <x:c r="B156" s="2" t="str">
+      <x:c r="B156" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C156" s="2" t="str">
+      <x:c r="C156" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D156" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E156" s="2"/>
+      <x:c r="D156" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E156" s="14"/>
     </x:row>
     <x:row r="157" ht="22" customHeight="1">
-      <x:c r="A157" s="2" t="str">
+      <x:c r="A157" s="14" t="str">
         <x:v>1 (42).docx</x:v>
       </x:c>
-      <x:c r="B157" s="2" t="str">
+      <x:c r="B157" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C157" s="2" t="str">
+      <x:c r="C157" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D157" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E157" s="2"/>
+      <x:c r="D157" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E157" s="14"/>
     </x:row>
     <x:row r="158" ht="22" customHeight="1">
-      <x:c r="A158" s="2" t="str">
+      <x:c r="A158" s="14" t="str">
         <x:v>1 (43).docx</x:v>
       </x:c>
-      <x:c r="B158" s="2" t="str">
+      <x:c r="B158" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C158" s="2" t="str">
+      <x:c r="C158" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D158" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E158" s="2"/>
+      <x:c r="D158" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E158" s="14"/>
     </x:row>
     <x:row r="159" ht="22" customHeight="1">
-      <x:c r="A159" s="2" t="str">
+      <x:c r="A159" s="14" t="str">
         <x:v>1 (44).docx</x:v>
       </x:c>
-      <x:c r="B159" s="2" t="str">
+      <x:c r="B159" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C159" s="2" t="str">
+      <x:c r="C159" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D159" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E159" s="2"/>
+      <x:c r="D159" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E159" s="14"/>
     </x:row>
     <x:row r="160" ht="22" customHeight="1">
-      <x:c r="A160" s="2" t="str">
+      <x:c r="A160" s="14" t="str">
         <x:v>1 (45).docx</x:v>
       </x:c>
-      <x:c r="B160" s="2" t="str">
+      <x:c r="B160" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C160" s="2" t="str">
+      <x:c r="C160" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D160" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E160" s="2"/>
+      <x:c r="D160" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E160" s="14"/>
     </x:row>
     <x:row r="161" ht="22" customHeight="1">
-      <x:c r="A161" s="2" t="str">
+      <x:c r="A161" s="14" t="str">
         <x:v>1 (46).docx</x:v>
       </x:c>
-      <x:c r="B161" s="2" t="str">
+      <x:c r="B161" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C161" s="2" t="str">
+      <x:c r="C161" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D161" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E161" s="2"/>
+      <x:c r="D161" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E161" s="14"/>
     </x:row>
     <x:row r="162" ht="22" customHeight="1">
-      <x:c r="A162" s="2" t="str">
+      <x:c r="A162" s="14" t="str">
         <x:v>1 (47).docx</x:v>
       </x:c>
-      <x:c r="B162" s="2" t="str">
+      <x:c r="B162" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C162" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D162" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E162" s="14"/>
+    </x:row>
+    <x:row r="163" ht="22" customHeight="1">
+      <x:c r="A163" s="14" t="str">
+        <x:v>1 (48).docx</x:v>
+      </x:c>
+      <x:c r="B163" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C163" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D163" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E163" s="14"/>
+    </x:row>
+    <x:row r="164" ht="22" customHeight="1">
+      <x:c r="A164" s="14" t="str">
+        <x:v>1 (49).docx</x:v>
+      </x:c>
+      <x:c r="B164" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C162" s="2"/>
-      <x:c r="D162" s="2" t="str">
-        <x:v>author_verification_required</x:v>
-      </x:c>
-      <x:c r="E162" s="2" t="str">
-        <x:v>AC base A (%): passing_19_1mm: 90.6 outside 60–90 | AC base B (%): passing_19_1mm: 90.6 outside 70–90; passing_2_0mm: 28.2 outside 30–47; passing_0_425mm: 10.4 outside 15–26; passing_0_177mm: 6.4 outside 7–17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" ht="22" customHeight="1">
-      <x:c r="A163" s="2" t="str">
-        <x:v>1 (48).docx</x:v>
-      </x:c>
-      <x:c r="B163" s="2" t="str">
+      <x:c r="C164" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D164" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E164" s="14"/>
+    </x:row>
+    <x:row r="165" ht="22" customHeight="1">
+      <x:c r="A165" s="14" t="str">
+        <x:v>1 (5).docx</x:v>
+      </x:c>
+      <x:c r="B165" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C165" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D165" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E165" s="14"/>
+    </x:row>
+    <x:row r="166" ht="22" customHeight="1">
+      <x:c r="A166" s="14" t="str">
+        <x:v>1 (50).docx</x:v>
+      </x:c>
+      <x:c r="B166" s="14" t="str">
+        <x:v>ac_base_course</x:v>
+      </x:c>
+      <x:c r="C166" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D166" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E166" s="14"/>
+    </x:row>
+    <x:row r="167" ht="22" customHeight="1">
+      <x:c r="A167" s="14" t="str">
+        <x:v>1 (51).docx</x:v>
+      </x:c>
+      <x:c r="B167" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C167" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D167" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E167" s="14"/>
+    </x:row>
+    <x:row r="168" ht="22" customHeight="1">
+      <x:c r="A168" s="14" t="str">
+        <x:v>1 (52).docx</x:v>
+      </x:c>
+      <x:c r="B168" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C168" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D168" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E168" s="14"/>
+    </x:row>
+    <x:row r="169" ht="22" customHeight="1">
+      <x:c r="A169" s="14" t="str">
+        <x:v>1 (53).docx</x:v>
+      </x:c>
+      <x:c r="B169" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C169" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D169" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E169" s="14"/>
+    </x:row>
+    <x:row r="170" ht="22" customHeight="1">
+      <x:c r="A170" s="14" t="str">
+        <x:v>1 (54).docx</x:v>
+      </x:c>
+      <x:c r="B170" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C163" s="2" t="str">
+      <x:c r="C170" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D163" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E163" s="2"/>
-    </x:row>
-    <x:row r="164" ht="22" customHeight="1">
-      <x:c r="A164" s="2" t="str">
-        <x:v>1 (49).docx</x:v>
-      </x:c>
-      <x:c r="B164" s="2" t="str">
+      <x:c r="D170" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E170" s="14"/>
+    </x:row>
+    <x:row r="171" ht="22" customHeight="1">
+      <x:c r="A171" s="14" t="str">
+        <x:v>1 (55).docx</x:v>
+      </x:c>
+      <x:c r="B171" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C164" s="2" t="str">
+      <x:c r="C171" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D164" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E164" s="2"/>
-    </x:row>
-    <x:row r="165" ht="22" customHeight="1">
-      <x:c r="A165" s="2" t="str">
-        <x:v>1 (5).docx</x:v>
-      </x:c>
-      <x:c r="B165" s="2" t="str">
+      <x:c r="D171" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E171" s="14"/>
+    </x:row>
+    <x:row r="172" ht="22" customHeight="1">
+      <x:c r="A172" s="14" t="str">
+        <x:v>1 (56).docx</x:v>
+      </x:c>
+      <x:c r="B172" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C165" s="2" t="str">
+      <x:c r="C172" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D165" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E165" s="2"/>
-    </x:row>
-    <x:row r="166" ht="22" customHeight="1">
-      <x:c r="A166" s="2" t="str">
-        <x:v>1 (50).docx</x:v>
-      </x:c>
-      <x:c r="B166" s="2" t="str">
+      <x:c r="D172" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E172" s="14"/>
+    </x:row>
+    <x:row r="173" ht="22" customHeight="1">
+      <x:c r="A173" s="14" t="str">
+        <x:v>1 (57).docx</x:v>
+      </x:c>
+      <x:c r="B173" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C173" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D173" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E173" s="14"/>
+    </x:row>
+    <x:row r="174" ht="22" customHeight="1">
+      <x:c r="A174" s="14" t="str">
+        <x:v>1 (58).docx</x:v>
+      </x:c>
+      <x:c r="B174" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C166" s="2" t="str">
+      <x:c r="C174" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D166" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E166" s="2"/>
-    </x:row>
-    <x:row r="167" ht="22" customHeight="1">
-      <x:c r="A167" s="2" t="str">
-        <x:v>1 (51).docx</x:v>
-      </x:c>
-      <x:c r="B167" s="2" t="str">
+      <x:c r="D174" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E174" s="14"/>
+    </x:row>
+    <x:row r="175" ht="22" customHeight="1">
+      <x:c r="A175" s="14" t="str">
+        <x:v>1 (59).docx</x:v>
+      </x:c>
+      <x:c r="B175" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C175" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D175" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E175" s="14"/>
+    </x:row>
+    <x:row r="176" ht="22" customHeight="1">
+      <x:c r="A176" s="14" t="str">
+        <x:v>1 (6).docx</x:v>
+      </x:c>
+      <x:c r="B176" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C176" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D176" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E176" s="14"/>
+    </x:row>
+    <x:row r="177" ht="22" customHeight="1">
+      <x:c r="A177" s="14" t="str">
+        <x:v>1 (60).docx</x:v>
+      </x:c>
+      <x:c r="B177" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C177" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D177" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E177" s="14"/>
+    </x:row>
+    <x:row r="178" ht="22" customHeight="1">
+      <x:c r="A178" s="14" t="str">
+        <x:v>1 (61).docx</x:v>
+      </x:c>
+      <x:c r="B178" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C167" s="2"/>
-      <x:c r="D167" s="2" t="str">
-        <x:v>author_verification_required</x:v>
-      </x:c>
-      <x:c r="E167" s="2" t="str">
-        <x:v>AC base A (%): passing_19_1mm: 91.5 outside 60–90 | AC base B (%): passing_19_1mm: 91.5 outside 70–90; passing_2_0mm: 25 outside 30–47; passing_0_425mm: 11.2 outside 15–26; passing_0_177mm: 6.9 outside 7–17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" ht="22" customHeight="1">
-      <x:c r="A168" s="2" t="str">
-        <x:v>1 (52).docx</x:v>
-      </x:c>
-      <x:c r="B168" s="2" t="str">
+      <x:c r="C178" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D178" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E178" s="14"/>
+    </x:row>
+    <x:row r="179" ht="22" customHeight="1">
+      <x:c r="A179" s="14" t="str">
+        <x:v>1 (62).docx</x:v>
+      </x:c>
+      <x:c r="B179" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C179" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D179" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E179" s="14"/>
+    </x:row>
+    <x:row r="180" ht="22" customHeight="1">
+      <x:c r="A180" s="14" t="str">
+        <x:v>1 (63).docx</x:v>
+      </x:c>
+      <x:c r="B180" s="14" t="str">
+        <x:v>ac_base_course</x:v>
+      </x:c>
+      <x:c r="C180" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D180" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E180" s="14"/>
+    </x:row>
+    <x:row r="181" ht="22" customHeight="1">
+      <x:c r="A181" s="14" t="str">
+        <x:v>1 (64).docx</x:v>
+      </x:c>
+      <x:c r="B181" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C181" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D181" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E181" s="14"/>
+    </x:row>
+    <x:row r="182" ht="22" customHeight="1">
+      <x:c r="A182" s="14" t="str">
+        <x:v>1 (65).docx</x:v>
+      </x:c>
+      <x:c r="B182" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C168" s="2" t="str">
+      <x:c r="C182" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D168" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E168" s="2"/>
-    </x:row>
-    <x:row r="169" ht="22" customHeight="1">
-      <x:c r="A169" s="2" t="str">
-        <x:v>1 (53).docx</x:v>
-      </x:c>
-      <x:c r="B169" s="2" t="str">
+      <x:c r="D182" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E182" s="14"/>
+    </x:row>
+    <x:row r="183" ht="22" customHeight="1">
+      <x:c r="A183" s="14" t="str">
+        <x:v>1 (66).docx</x:v>
+      </x:c>
+      <x:c r="B183" s="14" t="str">
+        <x:v>ac_base_course</x:v>
+      </x:c>
+      <x:c r="C183" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D183" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E183" s="14"/>
+    </x:row>
+    <x:row r="184" ht="22" customHeight="1">
+      <x:c r="A184" s="14" t="str">
+        <x:v>1 (67).docx</x:v>
+      </x:c>
+      <x:c r="B184" s="14" t="str">
+        <x:v>ac_base_course</x:v>
+      </x:c>
+      <x:c r="C184" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D184" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E184" s="14"/>
+    </x:row>
+    <x:row r="185" ht="22" customHeight="1">
+      <x:c r="A185" s="14" t="str">
+        <x:v>1 (68).docx</x:v>
+      </x:c>
+      <x:c r="B185" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C169" s="2" t="str">
+      <x:c r="C185" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D169" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E169" s="2"/>
-    </x:row>
-    <x:row r="170" ht="22" customHeight="1">
-      <x:c r="A170" s="2" t="str">
-        <x:v>1 (54).docx</x:v>
-      </x:c>
-      <x:c r="B170" s="2" t="str">
+      <x:c r="D185" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E185" s="14"/>
+    </x:row>
+    <x:row r="186" ht="22" customHeight="1">
+      <x:c r="A186" s="14" t="str">
+        <x:v>1 (69).docx</x:v>
+      </x:c>
+      <x:c r="B186" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C170" s="2" t="str">
+      <x:c r="C186" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D170" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E170" s="2"/>
-    </x:row>
-    <x:row r="171" ht="22" customHeight="1">
-      <x:c r="A171" s="2" t="str">
-        <x:v>1 (55).docx</x:v>
-      </x:c>
-      <x:c r="B171" s="2" t="str">
+      <x:c r="D186" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E186" s="14"/>
+    </x:row>
+    <x:row r="187" ht="22" customHeight="1">
+      <x:c r="A187" s="14" t="str">
+        <x:v>1 (7).docx</x:v>
+      </x:c>
+      <x:c r="B187" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C187" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D187" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E187" s="14"/>
+    </x:row>
+    <x:row r="188" ht="22" customHeight="1">
+      <x:c r="A188" s="14" t="str">
+        <x:v>1 (70).docx</x:v>
+      </x:c>
+      <x:c r="B188" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C188" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D188" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E188" s="14"/>
+    </x:row>
+    <x:row r="189" ht="22" customHeight="1">
+      <x:c r="A189" s="14" t="str">
+        <x:v>1 (71).docx</x:v>
+      </x:c>
+      <x:c r="B189" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C189" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D189" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E189" s="14"/>
+    </x:row>
+    <x:row r="190" ht="22" customHeight="1">
+      <x:c r="A190" s="14" t="str">
+        <x:v>1 (72).docx</x:v>
+      </x:c>
+      <x:c r="B190" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C171" s="2" t="str">
+      <x:c r="C190" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D171" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E171" s="2"/>
-    </x:row>
-    <x:row r="172" ht="22" customHeight="1">
-      <x:c r="A172" s="2" t="str">
-        <x:v>1 (56).docx</x:v>
-      </x:c>
-      <x:c r="B172" s="2" t="str">
+      <x:c r="D190" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E190" s="14"/>
+    </x:row>
+    <x:row r="191" ht="22" customHeight="1">
+      <x:c r="A191" s="14" t="str">
+        <x:v>1 (73).docx</x:v>
+      </x:c>
+      <x:c r="B191" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C191" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D191" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E191" s="14"/>
+    </x:row>
+    <x:row r="192" ht="22" customHeight="1">
+      <x:c r="A192" s="14" t="str">
+        <x:v>1 (75).docx</x:v>
+      </x:c>
+      <x:c r="B192" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C172" s="2" t="str">
+      <x:c r="C192" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D172" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E172" s="2"/>
-    </x:row>
-    <x:row r="173" ht="22" customHeight="1">
-      <x:c r="A173" s="2" t="str">
-        <x:v>1 (57).docx</x:v>
-      </x:c>
-      <x:c r="B173" s="2" t="str">
+      <x:c r="D192" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E192" s="14"/>
+    </x:row>
+    <x:row r="193" ht="22" customHeight="1">
+      <x:c r="A193" s="14" t="str">
+        <x:v>1 (76).docx</x:v>
+      </x:c>
+      <x:c r="B193" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C193" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D193" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E193" s="14"/>
+    </x:row>
+    <x:row r="194" ht="22" customHeight="1">
+      <x:c r="A194" s="14" t="str">
+        <x:v>1 (78).docx</x:v>
+      </x:c>
+      <x:c r="B194" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C194" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D194" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E194" s="14"/>
+    </x:row>
+    <x:row r="195" ht="22" customHeight="1">
+      <x:c r="A195" s="14" t="str">
+        <x:v>1 (79).docx</x:v>
+      </x:c>
+      <x:c r="B195" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C195" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D195" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E195" s="14"/>
+    </x:row>
+    <x:row r="196" ht="22" customHeight="1">
+      <x:c r="A196" s="14" t="str">
+        <x:v>1 (8).docx</x:v>
+      </x:c>
+      <x:c r="B196" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C173" s="2"/>
-      <x:c r="D173" s="2" t="str">
-        <x:v>author_verification_required</x:v>
-      </x:c>
-      <x:c r="E173" s="2" t="str">
-        <x:v>AC base A (%): passing_19_1mm: 90.3 outside 60–90 | AC base B (%): passing_19_1mm: 90.3 outside 70–90; passing_0_425mm: 11.2 outside 15–26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" ht="22" customHeight="1">
-      <x:c r="A174" s="2" t="str">
-        <x:v>1 (58).docx</x:v>
-      </x:c>
-      <x:c r="B174" s="2" t="str">
+      <x:c r="C196" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D196" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E196" s="14"/>
+    </x:row>
+    <x:row r="197" ht="22" customHeight="1">
+      <x:c r="A197" s="14" t="str">
+        <x:v>1 (80).docx</x:v>
+      </x:c>
+      <x:c r="B197" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C197" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D197" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E197" s="14"/>
+    </x:row>
+    <x:row r="198" ht="22" customHeight="1">
+      <x:c r="A198" s="14" t="str">
+        <x:v>1 (81).docx</x:v>
+      </x:c>
+      <x:c r="B198" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C174" s="2" t="str">
+      <x:c r="C198" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D174" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E174" s="2"/>
-    </x:row>
-    <x:row r="175" ht="22" customHeight="1">
-      <x:c r="A175" s="2" t="str">
-        <x:v>1 (59).docx</x:v>
-      </x:c>
-      <x:c r="B175" s="2" t="str">
+      <x:c r="D198" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E198" s="14"/>
+    </x:row>
+    <x:row r="199" ht="22" customHeight="1">
+      <x:c r="A199" s="14" t="str">
+        <x:v>1 (82).docx</x:v>
+      </x:c>
+      <x:c r="B199" s="14" t="str">
+        <x:v>ac_base_course</x:v>
+      </x:c>
+      <x:c r="C199" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D199" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E199" s="14"/>
+    </x:row>
+    <x:row r="200" ht="22" customHeight="1">
+      <x:c r="A200" s="14" t="str">
+        <x:v>1 (83).docx</x:v>
+      </x:c>
+      <x:c r="B200" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C200" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D200" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E200" s="14"/>
+    </x:row>
+    <x:row r="201" ht="22" customHeight="1">
+      <x:c r="A201" s="14" t="str">
+        <x:v>1 (84).docx</x:v>
+      </x:c>
+      <x:c r="B201" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C175" s="2" t="str">
+      <x:c r="C201" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D175" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E175" s="2"/>
-    </x:row>
-    <x:row r="176" ht="22" customHeight="1">
-      <x:c r="A176" s="2" t="str">
-        <x:v>1 (6).docx</x:v>
-      </x:c>
-      <x:c r="B176" s="2" t="str">
+      <x:c r="D201" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E201" s="14"/>
+    </x:row>
+    <x:row r="202" ht="22" customHeight="1">
+      <x:c r="A202" s="14" t="str">
+        <x:v>1 (85).docx</x:v>
+      </x:c>
+      <x:c r="B202" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C176" s="2" t="str">
+      <x:c r="C202" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D176" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E176" s="2"/>
-    </x:row>
-    <x:row r="177" ht="22" customHeight="1">
-      <x:c r="A177" s="2" t="str">
-        <x:v>1 (60).docx</x:v>
-      </x:c>
-      <x:c r="B177" s="2" t="str">
+      <x:c r="D202" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E202" s="14"/>
+    </x:row>
+    <x:row r="203" ht="22" customHeight="1">
+      <x:c r="A203" s="14" t="str">
+        <x:v>1 (86).docx</x:v>
+      </x:c>
+      <x:c r="B203" s="14" t="str">
+        <x:v>ac_base_course</x:v>
+      </x:c>
+      <x:c r="C203" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D203" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E203" s="14"/>
+    </x:row>
+    <x:row r="204" ht="22" customHeight="1">
+      <x:c r="A204" s="14" t="str">
+        <x:v>1 (87).docx</x:v>
+      </x:c>
+      <x:c r="B204" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C177" s="2" t="str">
+      <x:c r="C204" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D177" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E177" s="2"/>
-    </x:row>
-    <x:row r="178" ht="22" customHeight="1">
-      <x:c r="A178" s="2" t="str">
-        <x:v>1 (61).docx</x:v>
-      </x:c>
-      <x:c r="B178" s="2" t="str">
+      <x:c r="D204" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E204" s="14"/>
+    </x:row>
+    <x:row r="205" ht="22" customHeight="1">
+      <x:c r="A205" s="14" t="str">
+        <x:v>1 (88).docx</x:v>
+      </x:c>
+      <x:c r="B205" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C178" s="2" t="str">
+      <x:c r="C205" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D178" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E178" s="2"/>
-    </x:row>
-    <x:row r="179" ht="22" customHeight="1">
-      <x:c r="A179" s="2" t="str">
-        <x:v>1 (62).docx</x:v>
-      </x:c>
-      <x:c r="B179" s="2" t="str">
+      <x:c r="D205" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E205" s="14"/>
+    </x:row>
+    <x:row r="206" ht="22" customHeight="1">
+      <x:c r="A206" s="14" t="str">
+        <x:v>1 (89).docx</x:v>
+      </x:c>
+      <x:c r="B206" s="14" t="str">
+        <x:v>ac_base_course</x:v>
+      </x:c>
+      <x:c r="C206" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D206" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E206" s="14"/>
+    </x:row>
+    <x:row r="207" ht="22" customHeight="1">
+      <x:c r="A207" s="14" t="str">
+        <x:v>1 (9).docx</x:v>
+      </x:c>
+      <x:c r="B207" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C179" s="2" t="str">
+      <x:c r="C207" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D179" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E179" s="2"/>
-    </x:row>
-    <x:row r="180" ht="22" customHeight="1">
-      <x:c r="A180" s="2" t="str">
-        <x:v>1 (63).docx</x:v>
-      </x:c>
-      <x:c r="B180" s="2" t="str">
+      <x:c r="D207" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E207" s="14"/>
+    </x:row>
+    <x:row r="208" ht="22" customHeight="1">
+      <x:c r="A208" s="14" t="str">
+        <x:v>1 (90).docx</x:v>
+      </x:c>
+      <x:c r="B208" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C208" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D208" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E208" s="14"/>
+    </x:row>
+    <x:row r="209" ht="22" customHeight="1">
+      <x:c r="A209" s="14" t="str">
+        <x:v>1 (91).docx</x:v>
+      </x:c>
+      <x:c r="B209" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C209" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D209" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E209" s="14"/>
+    </x:row>
+    <x:row r="210" ht="22" customHeight="1">
+      <x:c r="A210" s="14" t="str">
+        <x:v>1 (92).docx</x:v>
+      </x:c>
+      <x:c r="B210" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C210" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D210" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E210" s="14"/>
+    </x:row>
+    <x:row r="211" ht="22" customHeight="1">
+      <x:c r="A211" s="14" t="str">
+        <x:v>1 (93).docx</x:v>
+      </x:c>
+      <x:c r="B211" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C180" s="2" t="str">
+      <x:c r="C211" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D180" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E180" s="2"/>
-    </x:row>
-    <x:row r="181" ht="22" customHeight="1">
-      <x:c r="A181" s="2" t="str">
-        <x:v>1 (64).docx</x:v>
-      </x:c>
-      <x:c r="B181" s="2" t="str">
+      <x:c r="D211" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E211" s="14"/>
+    </x:row>
+    <x:row r="212" ht="22" customHeight="1">
+      <x:c r="A212" s="14" t="str">
+        <x:v>1 (94).docx</x:v>
+      </x:c>
+      <x:c r="B212" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C181" s="2" t="str">
+      <x:c r="C212" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D181" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E181" s="2"/>
-    </x:row>
-    <x:row r="182" ht="22" customHeight="1">
-      <x:c r="A182" s="2" t="str">
-        <x:v>1 (65).docx</x:v>
-      </x:c>
-      <x:c r="B182" s="2" t="str">
+      <x:c r="D212" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E212" s="14"/>
+    </x:row>
+    <x:row r="213" ht="22" customHeight="1">
+      <x:c r="A213" s="14" t="str">
+        <x:v>1 (95).docx</x:v>
+      </x:c>
+      <x:c r="B213" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C213" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D213" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E213" s="14"/>
+    </x:row>
+    <x:row r="214" ht="22" customHeight="1">
+      <x:c r="A214" s="14" t="str">
+        <x:v>1 (96).docx</x:v>
+      </x:c>
+      <x:c r="B214" s="14" t="str">
         <x:v>binder_course</x:v>
       </x:c>
-      <x:c r="C182" s="2" t="str">
+      <x:c r="C214" s="14" t="str">
         <x:v>Binder (%)</x:v>
       </x:c>
-      <x:c r="D182" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E182" s="2"/>
-    </x:row>
-    <x:row r="183" ht="22" customHeight="1">
-      <x:c r="A183" s="2" t="str">
-        <x:v>1 (66).docx</x:v>
-      </x:c>
-      <x:c r="B183" s="2" t="str">
+      <x:c r="D214" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E214" s="14"/>
+    </x:row>
+    <x:row r="215" ht="22" customHeight="1">
+      <x:c r="A215" s="14" t="str">
+        <x:v>1 (97).docx</x:v>
+      </x:c>
+      <x:c r="B215" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C183" s="2" t="str">
+      <x:c r="C215" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D183" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E183" s="2"/>
-    </x:row>
-    <x:row r="184" ht="22" customHeight="1">
-      <x:c r="A184" s="2" t="str">
-        <x:v>1 (67).docx</x:v>
-      </x:c>
-      <x:c r="B184" s="2" t="str">
+      <x:c r="D215" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E215" s="14"/>
+    </x:row>
+    <x:row r="216" ht="22" customHeight="1">
+      <x:c r="A216" s="14" t="str">
+        <x:v>1 (98).docx</x:v>
+      </x:c>
+      <x:c r="B216" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C216" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D216" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E216" s="14"/>
+    </x:row>
+    <x:row r="217" ht="22" customHeight="1">
+      <x:c r="A217" s="14" t="str">
+        <x:v>1 (99).docx</x:v>
+      </x:c>
+      <x:c r="B217" s="14" t="str">
+        <x:v>wearing_course</x:v>
+      </x:c>
+      <x:c r="C217" s="14" t="str">
+        <x:v>Wearing type 1 (%)</x:v>
+      </x:c>
+      <x:c r="D217" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E217" s="14"/>
+    </x:row>
+    <x:row r="218" ht="22" customHeight="1">
+      <x:c r="A218" s="14" t="str">
+        <x:v>1 (205).docx</x:v>
+      </x:c>
+      <x:c r="B218" s="14" t="str">
+        <x:v>binder_course</x:v>
+      </x:c>
+      <x:c r="C218" s="14" t="str">
+        <x:v>Binder (%)</x:v>
+      </x:c>
+      <x:c r="D218" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E218" s="14"/>
+    </x:row>
+    <x:row r="219" ht="22" customHeight="1">
+      <x:c r="A219" s="14" t="str">
+        <x:v>1 (206).docx</x:v>
+      </x:c>
+      <x:c r="B219" s="14" t="str">
         <x:v>ac_base_course</x:v>
       </x:c>
-      <x:c r="C184" s="2" t="str">
+      <x:c r="C219" s="14" t="str">
         <x:v>AC base A (%)</x:v>
       </x:c>
-      <x:c r="D184" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E184" s="2"/>
-    </x:row>
-    <x:row r="185" ht="22" customHeight="1">
-      <x:c r="A185" s="2" t="str">
-        <x:v>1 (68).docx</x:v>
-      </x:c>
-      <x:c r="B185" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C185" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D185" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E185" s="2"/>
-    </x:row>
-    <x:row r="186" ht="22" customHeight="1">
-      <x:c r="A186" s="2" t="str">
-        <x:v>1 (69).docx</x:v>
-      </x:c>
-      <x:c r="B186" s="2" t="str">
+      <x:c r="D219" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E219" s="14"/>
+    </x:row>
+    <x:row r="220" ht="22" customHeight="1">
+      <x:c r="A220" s="14" t="str">
+        <x:v>1 (207).docx</x:v>
+      </x:c>
+      <x:c r="B220" s="14" t="str">
+        <x:v>ac_base_course</x:v>
+      </x:c>
+      <x:c r="C220" s="14" t="str">
+        <x:v>AC base A (%)</x:v>
+      </x:c>
+      <x:c r="D220" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E220" s="14"/>
+    </x:row>
+    <x:row r="221" ht="22" customHeight="1">
+      <x:c r="A221" s="14" t="str">
+        <x:v>1 (208).docx</x:v>
+      </x:c>
+      <x:c r="B221" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C186" s="2" t="str">
+      <x:c r="C221" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D186" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E186" s="2"/>
-    </x:row>
-    <x:row r="187" ht="22" customHeight="1">
-      <x:c r="A187" s="2" t="str">
-        <x:v>1 (7).docx</x:v>
-      </x:c>
-      <x:c r="B187" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C187" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D187" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E187" s="2"/>
-    </x:row>
-    <x:row r="188" ht="22" customHeight="1">
-      <x:c r="A188" s="2" t="str">
-        <x:v>1 (70).docx</x:v>
-      </x:c>
-      <x:c r="B188" s="2" t="str">
+      <x:c r="D221" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E221" s="14"/>
+    </x:row>
+    <x:row r="222" ht="22" customHeight="1">
+      <x:c r="A222" s="14" t="str">
+        <x:v>1 (209).docx</x:v>
+      </x:c>
+      <x:c r="B222" s="14" t="str">
         <x:v>wearing_course</x:v>
       </x:c>
-      <x:c r="C188" s="2" t="str">
+      <x:c r="C222" s="14" t="str">
         <x:v>Wearing type 1 (%)</x:v>
       </x:c>
-      <x:c r="D188" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E188" s="2"/>
-    </x:row>
-    <x:row r="189" ht="22" customHeight="1">
-      <x:c r="A189" s="2" t="str">
-        <x:v>1 (71).docx</x:v>
-      </x:c>
-      <x:c r="B189" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C189" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D189" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E189" s="2"/>
-    </x:row>
-    <x:row r="190" ht="22" customHeight="1">
-      <x:c r="A190" s="2" t="str">
-        <x:v>1 (72).docx</x:v>
-      </x:c>
-      <x:c r="B190" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C190" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D190" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E190" s="2"/>
-    </x:row>
-    <x:row r="191" ht="22" customHeight="1">
-      <x:c r="A191" s="2" t="str">
-        <x:v>1 (73).docx</x:v>
-      </x:c>
-      <x:c r="B191" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C191" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D191" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E191" s="2"/>
-    </x:row>
-    <x:row r="192" ht="22" customHeight="1">
-      <x:c r="A192" s="2" t="str">
-        <x:v>1 (75).docx</x:v>
-      </x:c>
-      <x:c r="B192" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C192" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D192" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E192" s="2"/>
-    </x:row>
-    <x:row r="193" ht="22" customHeight="1">
-      <x:c r="A193" s="2" t="str">
-        <x:v>1 (76).docx</x:v>
-      </x:c>
-      <x:c r="B193" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C193" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D193" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E193" s="2"/>
-    </x:row>
-    <x:row r="194" ht="22" customHeight="1">
-      <x:c r="A194" s="2" t="str">
-        <x:v>1 (78).docx</x:v>
-      </x:c>
-      <x:c r="B194" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C194" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D194" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E194" s="2"/>
-    </x:row>
-    <x:row r="195" ht="22" customHeight="1">
-      <x:c r="A195" s="2" t="str">
-        <x:v>1 (79).docx</x:v>
-      </x:c>
-      <x:c r="B195" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C195" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D195" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E195" s="2"/>
-    </x:row>
-    <x:row r="196" ht="22" customHeight="1">
-      <x:c r="A196" s="2" t="str">
-        <x:v>1 (8).docx</x:v>
-      </x:c>
-      <x:c r="B196" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C196" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D196" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E196" s="2"/>
-    </x:row>
-    <x:row r="197" ht="22" customHeight="1">
-      <x:c r="A197" s="2" t="str">
-        <x:v>1 (80).docx</x:v>
-      </x:c>
-      <x:c r="B197" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C197" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D197" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E197" s="2"/>
-    </x:row>
-    <x:row r="198" ht="22" customHeight="1">
-      <x:c r="A198" s="2" t="str">
-        <x:v>1 (81).docx</x:v>
-      </x:c>
-      <x:c r="B198" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C198" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D198" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E198" s="2"/>
-    </x:row>
-    <x:row r="199" ht="22" customHeight="1">
-      <x:c r="A199" s="2" t="str">
-        <x:v>1 (82).docx</x:v>
-      </x:c>
-      <x:c r="B199" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C199" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D199" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E199" s="2"/>
-    </x:row>
-    <x:row r="200" ht="22" customHeight="1">
-      <x:c r="A200" s="2" t="str">
-        <x:v>1 (83).docx</x:v>
-      </x:c>
-      <x:c r="B200" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C200" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D200" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E200" s="2"/>
-    </x:row>
-    <x:row r="201" ht="22" customHeight="1">
-      <x:c r="A201" s="2" t="str">
-        <x:v>1 (84).docx</x:v>
-      </x:c>
-      <x:c r="B201" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C201" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D201" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E201" s="2"/>
-    </x:row>
-    <x:row r="202" ht="22" customHeight="1">
-      <x:c r="A202" s="2" t="str">
-        <x:v>1 (85).docx</x:v>
-      </x:c>
-      <x:c r="B202" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C202" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D202" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E202" s="2"/>
-    </x:row>
-    <x:row r="203" ht="22" customHeight="1">
-      <x:c r="A203" s="2" t="str">
-        <x:v>1 (86).docx</x:v>
-      </x:c>
-      <x:c r="B203" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C203" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D203" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E203" s="2"/>
-    </x:row>
-    <x:row r="204" ht="22" customHeight="1">
-      <x:c r="A204" s="2" t="str">
-        <x:v>1 (87).docx</x:v>
-      </x:c>
-      <x:c r="B204" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C204" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D204" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E204" s="2"/>
-    </x:row>
-    <x:row r="205" ht="22" customHeight="1">
-      <x:c r="A205" s="2" t="str">
-        <x:v>1 (88).docx</x:v>
-      </x:c>
-      <x:c r="B205" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C205" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D205" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E205" s="2"/>
-    </x:row>
-    <x:row r="206" ht="22" customHeight="1">
-      <x:c r="A206" s="2" t="str">
-        <x:v>1 (89).docx</x:v>
-      </x:c>
-      <x:c r="B206" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C206" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D206" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E206" s="2"/>
-    </x:row>
-    <x:row r="207" ht="22" customHeight="1">
-      <x:c r="A207" s="2" t="str">
-        <x:v>1 (9).docx</x:v>
-      </x:c>
-      <x:c r="B207" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C207" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D207" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E207" s="2"/>
-    </x:row>
-    <x:row r="208" ht="22" customHeight="1">
-      <x:c r="A208" s="2" t="str">
-        <x:v>1 (90).docx</x:v>
-      </x:c>
-      <x:c r="B208" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C208" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D208" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E208" s="2"/>
-    </x:row>
-    <x:row r="209" ht="22" customHeight="1">
-      <x:c r="A209" s="2" t="str">
-        <x:v>1 (91).docx</x:v>
-      </x:c>
-      <x:c r="B209" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C209" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D209" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E209" s="2"/>
-    </x:row>
-    <x:row r="210" ht="22" customHeight="1">
-      <x:c r="A210" s="2" t="str">
-        <x:v>1 (92).docx</x:v>
-      </x:c>
-      <x:c r="B210" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C210" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D210" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E210" s="2"/>
-    </x:row>
-    <x:row r="211" ht="22" customHeight="1">
-      <x:c r="A211" s="2" t="str">
-        <x:v>1 (93).docx</x:v>
-      </x:c>
-      <x:c r="B211" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C211" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D211" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E211" s="2"/>
-    </x:row>
-    <x:row r="212" ht="22" customHeight="1">
-      <x:c r="A212" s="2" t="str">
-        <x:v>1 (94).docx</x:v>
-      </x:c>
-      <x:c r="B212" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C212" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D212" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E212" s="2"/>
-    </x:row>
-    <x:row r="213" ht="22" customHeight="1">
-      <x:c r="A213" s="2" t="str">
-        <x:v>1 (95).docx</x:v>
-      </x:c>
-      <x:c r="B213" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C213" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D213" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E213" s="2"/>
-    </x:row>
-    <x:row r="214" ht="22" customHeight="1">
-      <x:c r="A214" s="2" t="str">
-        <x:v>1 (96).docx</x:v>
-      </x:c>
-      <x:c r="B214" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C214" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D214" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E214" s="2"/>
-    </x:row>
-    <x:row r="215" ht="22" customHeight="1">
-      <x:c r="A215" s="2" t="str">
-        <x:v>1 (97).docx</x:v>
-      </x:c>
-      <x:c r="B215" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C215" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D215" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E215" s="2"/>
-    </x:row>
-    <x:row r="216" ht="22" customHeight="1">
-      <x:c r="A216" s="2" t="str">
-        <x:v>1 (98).docx</x:v>
-      </x:c>
-      <x:c r="B216" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C216" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D216" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E216" s="2"/>
-    </x:row>
-    <x:row r="217" ht="22" customHeight="1">
-      <x:c r="A217" s="2" t="str">
-        <x:v>1 (99).docx</x:v>
-      </x:c>
-      <x:c r="B217" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C217" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D217" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E217" s="2"/>
-    </x:row>
-    <x:row r="218" ht="22" customHeight="1">
-      <x:c r="A218" s="2" t="str">
-        <x:v>1 (205).docx</x:v>
-      </x:c>
-      <x:c r="B218" s="2" t="str">
-        <x:v>binder_course</x:v>
-      </x:c>
-      <x:c r="C218" s="2" t="str">
-        <x:v>Binder (%)</x:v>
-      </x:c>
-      <x:c r="D218" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E218" s="2"/>
-    </x:row>
-    <x:row r="219" ht="22" customHeight="1">
-      <x:c r="A219" s="2" t="str">
-        <x:v>1 (206).docx</x:v>
-      </x:c>
-      <x:c r="B219" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C219" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D219" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E219" s="2"/>
-    </x:row>
-    <x:row r="220" ht="22" customHeight="1">
-      <x:c r="A220" s="2" t="str">
-        <x:v>1 (207).docx</x:v>
-      </x:c>
-      <x:c r="B220" s="2" t="str">
-        <x:v>ac_base_course</x:v>
-      </x:c>
-      <x:c r="C220" s="2" t="str">
-        <x:v>AC base A (%)</x:v>
-      </x:c>
-      <x:c r="D220" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E220" s="2"/>
-    </x:row>
-    <x:row r="221" ht="22" customHeight="1">
-      <x:c r="A221" s="2" t="str">
-        <x:v>1 (208).docx</x:v>
-      </x:c>
-      <x:c r="B221" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C221" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D221" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E221" s="2"/>
-    </x:row>
-    <x:row r="222" ht="22" customHeight="1">
-      <x:c r="A222" s="2" t="str">
-        <x:v>1 (209).docx</x:v>
-      </x:c>
-      <x:c r="B222" s="2" t="str">
-        <x:v>wearing_course</x:v>
-      </x:c>
-      <x:c r="C222" s="2" t="str">
-        <x:v>Wearing type 1 (%)</x:v>
-      </x:c>
-      <x:c r="D222" s="2" t="str">
-        <x:v>compatible_with_supplied_table</x:v>
-      </x:c>
-      <x:c r="E222" s="2"/>
+      <x:c r="D222" s="14" t="str">
+        <x:v>compatible_with_supplied_table</x:v>
+      </x:c>
+      <x:c r="E222" s="14"/>
     </x:row>
     <x:row r="223" ht="22" customHeight="1">
       <x:c r="A223" s="2"/>
@@ -28766,8 +28774,8 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16775ff5e0a2493d"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fd652ae22b746ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42c4e442002f4e6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R247a14f168b74ba6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29267,7 +29275,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8676cf4eb9ef4ca5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e80e2b47dfb4e57"/>
   </x:tableParts>
 </x:worksheet>
 </file>